--- a/database/event/4290/event_4290_evp_summary.xlsx
+++ b/database/event/4290/event_4290_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3242</v>
+        <v>5.8261</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7221</v>
+        <v>1.8844</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7295</v>
+        <v>1.8772</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3242</v>
+        <v>5.8261</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1453</v>
+        <v>1.6472</v>
       </c>
       <c r="G2" t="n">
         <v>4.1789</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1453</v>
+        <v>1.6472</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9283</v>
+        <v>1.3351</v>
       </c>
       <c r="J2" t="n">
         <v>4.1789</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1072</v>
+        <v>5.513999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>208</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9593</v>
+        <v>5.3733</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6041</v>
+        <v>1.738</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5821</v>
+        <v>1.6968</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9593</v>
+        <v>5.3733</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3335</v>
+        <v>3.7554</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6258</v>
+        <v>1.6179</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3335</v>
+        <v>3.7554</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0809</v>
+        <v>3.0438</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6258</v>
+        <v>1.6179</v>
       </c>
       <c r="K3" t="n">
         <v>44</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7067</v>
+        <v>4.6617</v>
       </c>
       <c r="N3" t="n">
         <v>166</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.435</v>
+        <v>5.2327</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4345</v>
+        <v>1.6925</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3703</v>
+        <v>1.6408</v>
       </c>
       <c r="E4" t="n">
-        <v>4.435</v>
+        <v>5.2327</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8171</v>
+        <v>1.6069</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6179</v>
+        <v>3.6258</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8171</v>
+        <v>1.6069</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2833</v>
+        <v>1.3024</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6179</v>
+        <v>3.6258</v>
       </c>
       <c r="K4" t="n">
         <v>44</v>
@@ -621,7 +621,7 @@
         <v>122</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9012</v>
+        <v>4.9282</v>
       </c>
       <c r="N4" t="n">
         <v>166</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0062</v>
+        <v>4.2062</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2958</v>
+        <v>1.3605</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1971</v>
+        <v>1.2318</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0062</v>
+        <v>4.2062</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5953</v>
+        <v>1.7953</v>
       </c>
       <c r="G5" t="n">
         <v>2.4109</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5953</v>
+        <v>1.7953</v>
       </c>
       <c r="I5" t="n">
-        <v>1.293</v>
+        <v>1.4551</v>
       </c>
       <c r="J5" t="n">
         <v>2.4109</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7039</v>
+        <v>3.866</v>
       </c>
       <c r="N5" t="n">
         <v>166</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3552</v>
+        <v>3.9203</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0852</v>
+        <v>1.268</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9341</v>
+        <v>1.1179</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3552</v>
+        <v>3.9203</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0827</v>
+        <v>1.6478</v>
       </c>
       <c r="G6" t="n">
         <v>2.2725</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0827</v>
+        <v>1.6478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8776</v>
+        <v>1.3356</v>
       </c>
       <c r="J6" t="n">
         <v>2.2725</v>
@@ -713,7 +713,7 @@
         <v>157</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1501</v>
+        <v>3.6081</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9936</v>
+        <v>3.5235</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9683</v>
+        <v>1.1397</v>
       </c>
       <c r="D7" t="n">
-        <v>0.788</v>
+        <v>0.9599</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9936</v>
+        <v>3.5235</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5907</v>
+        <v>1.1206</v>
       </c>
       <c r="G7" t="n">
         <v>2.4029</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5907</v>
+        <v>1.1206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4787</v>
+        <v>0.9083</v>
       </c>
       <c r="J7" t="n">
         <v>2.4029</v>
@@ -759,7 +759,7 @@
         <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8816</v>
+        <v>3.3112</v>
       </c>
       <c r="N7" t="n">
         <v>208</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4617</v>
+        <v>2.625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7962</v>
+        <v>0.849</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.6019</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4617</v>
+        <v>2.625</v>
       </c>
       <c r="F8" t="n">
-        <v>1.036</v>
+        <v>1.1993</v>
       </c>
       <c r="G8" t="n">
         <v>1.4257</v>
       </c>
       <c r="H8" t="n">
-        <v>1.036</v>
+        <v>1.1993</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8397</v>
+        <v>0.9721</v>
       </c>
       <c r="J8" t="n">
         <v>1.4257</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2654</v>
+        <v>2.3978</v>
       </c>
       <c r="N8" t="n">
         <v>166</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8716</v>
+        <v>2.0184</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6054</v>
+        <v>0.6528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3347</v>
+        <v>0.3602</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8716</v>
+        <v>2.0184</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2626</v>
+        <v>2.0184</v>
       </c>
       <c r="G9" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2626</v>
+        <v>2.0184</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0234</v>
+        <v>2.0184</v>
       </c>
       <c r="J9" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L9" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6324</v>
+        <v>2.0184</v>
       </c>
       <c r="N9" t="n">
-        <v>208</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7453</v>
+        <v>1.9661</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5645</v>
+        <v>0.6359</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2837</v>
+        <v>0.3394</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7453</v>
+        <v>1.9661</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7453</v>
+        <v>1.3571</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7453</v>
+        <v>1.3571</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7453</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="K10" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7453</v>
+        <v>1.709</v>
       </c>
       <c r="N10" t="n">
-        <v>83</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -916,7 +916,7 @@
         <v>0.5527</v>
       </c>
       <c r="D11" t="n">
-        <v>0.269</v>
+        <v>0.2369</v>
       </c>
       <c r="E11" t="n">
         <v>1.7089</v>
@@ -952,170 +952,170 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3253</v>
+        <v>1.502</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4287</v>
+        <v>0.4858</v>
       </c>
       <c r="D12" t="n">
-        <v>0.114</v>
+        <v>0.1545</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3253</v>
+        <v>1.502</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0125</v>
+        <v>1.502</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3128</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0125</v>
+        <v>1.502</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8207</v>
+        <v>1.502</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3128</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>83</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="N12" t="n">
         <v>83</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.1335</v>
-      </c>
-      <c r="N12" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2245</v>
+        <v>1.4502</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3961</v>
+        <v>0.4691</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0733</v>
+        <v>0.1338</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2245</v>
+        <v>1.4502</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2245</v>
+        <v>1.1374</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.3128</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2245</v>
+        <v>1.1374</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2245</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.3128</v>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2245</v>
+        <v>1.2347</v>
       </c>
       <c r="N13" t="n">
-        <v>78</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2797</v>
+        <v>0.451</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0721</v>
+        <v>0.1117</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8646</v>
+        <v>1.3945</v>
       </c>
       <c r="N14" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2692</v>
+        <v>0.2958</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0851</v>
+        <v>-0.0795</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8324</v>
+        <v>0.9146</v>
       </c>
       <c r="N15" t="n">
         <v>78</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2207</v>
+        <v>0.2727</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1458</v>
+        <v>-0.1081</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6822</v>
+        <v>0.843</v>
       </c>
       <c r="N16" t="n">
         <v>78</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1756</v>
+        <v>0.2692</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2021</v>
+        <v>-0.1124</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5683</v>
+        <v>0.8577</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0255</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5683</v>
+        <v>0.8577</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4606</v>
+        <v>0.6952</v>
       </c>
       <c r="J17" t="n">
         <v>-0.0255</v>
@@ -1219,7 +1219,7 @@
         <v>48</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4351</v>
+        <v>0.6697000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>131</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3503</v>
+        <v>0.527</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1133</v>
+        <v>0.1705</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2798</v>
+        <v>-0.234</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3503</v>
+        <v>0.527</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3503</v>
+        <v>1.527</v>
       </c>
       <c r="G18" t="n">
         <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3503</v>
+        <v>1.527</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0945</v>
+        <v>1.2377</v>
       </c>
       <c r="J18" t="n">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09450000000000003</v>
+        <v>0.2377</v>
       </c>
       <c r="N18" t="n">
         <v>182</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0694</v>
+        <v>0.1078</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3347</v>
+        <v>-0.3112</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2146</v>
+        <v>0.3332</v>
       </c>
       <c r="N19" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0673</v>
+        <v>0.0694</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3373</v>
+        <v>-0.3584</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2082</v>
+        <v>0.2146</v>
       </c>
       <c r="N20" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         <v>0.0672</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3375</v>
+        <v>-0.3612</v>
       </c>
       <c r="E21" t="n">
         <v>0.2077</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0019</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.419</v>
+        <v>-0.4332</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0059</v>
+        <v>0.027</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0334</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4631</v>
+        <v>-0.4851</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1033</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0355</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4657</v>
+        <v>-0.4876</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1097</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0419</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4737</v>
+        <v>-0.4955</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1296</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0453</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.478</v>
+        <v>-0.4998</v>
       </c>
       <c r="E26" t="n">
         <v>-0.1402</v>
@@ -1652,7 +1652,7 @@
         <v>-0.08069999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5222</v>
+        <v>-0.5433</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2495</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1309</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5849</v>
+        <v>-0.6052</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4048</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1791</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.645</v>
+        <v>-0.6645</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5536</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6621</v>
+        <v>-0.5626</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2142</v>
+        <v>-0.182</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6888</v>
+        <v>-0.6681</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6621</v>
+        <v>-0.5626</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3379</v>
+        <v>0.4374</v>
       </c>
       <c r="G30" t="n">
         <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3379</v>
+        <v>0.4374</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2738</v>
+        <v>0.3545</v>
       </c>
       <c r="J30" t="n">
         <v>-1</v>
@@ -1817,7 +1817,7 @@
         <v>83</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7262</v>
+        <v>-0.6455</v>
       </c>
       <c r="N30" t="n">
         <v>166</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2948</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7895</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>-0.9114</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9782</v>
+        <v>-0.9643</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3164</v>
+        <v>-0.3119</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8165</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9782</v>
+        <v>-0.9643</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6081</v>
+        <v>-0.5942</v>
       </c>
       <c r="G32" t="n">
         <v>-0.3701</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6081</v>
+        <v>-0.5942</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4929</v>
+        <v>-0.4816</v>
       </c>
       <c r="J32" t="n">
         <v>-0.3701</v>
@@ -1909,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.863</v>
+        <v>-0.8516999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>166</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3475</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8554</v>
+        <v>-0.872</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0744</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3539</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8633</v>
+        <v>-0.8798</v>
       </c>
       <c r="E34" t="n">
         <v>-1.094</v>
@@ -2020,7 +2020,7 @@
         <v>-0.362</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8898</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1191</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3891</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9073</v>
+        <v>-0.9232</v>
       </c>
       <c r="E36" t="n">
         <v>-1.203</v>
@@ -2112,7 +2112,7 @@
         <v>-0.412</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9514</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2739</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3431</v>
+        <v>-1.2799</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4344</v>
+        <v>-0.414</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9639</v>
+        <v>-0.9538</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3431</v>
+        <v>-1.2799</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2477</v>
+        <v>0.3109</v>
       </c>
       <c r="G38" t="n">
         <v>-1.5908</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2477</v>
+        <v>0.3109</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2008</v>
+        <v>0.252</v>
       </c>
       <c r="J38" t="n">
         <v>-1.5908</v>
@@ -2185,7 +2185,7 @@
         <v>122</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.39</v>
+        <v>-1.3388</v>
       </c>
       <c r="N38" t="n">
         <v>166</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4706</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0092</v>
+        <v>-1.0236</v>
       </c>
       <c r="E39" t="n">
         <v>-1.4551</v>
@@ -2250,7 +2250,7 @@
         <v>-0.7631</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3745</v>
+        <v>-1.3839</v>
       </c>
       <c r="E40" t="n">
         <v>-2.3594</v>

--- a/database/event/4290/event_4290_evp_summary.xlsx
+++ b/database/event/4290/event_4290_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8261</v>
+        <v>5.9418</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8844</v>
+        <v>1.9219</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8772</v>
+        <v>2.0444</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8261</v>
+        <v>5.9418</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6472</v>
+        <v>2.2246</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1789</v>
+        <v>3.7172</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6472</v>
+        <v>2.3519</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3351</v>
+        <v>1.2229</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1789</v>
+        <v>3.7172</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>5.513999999999999</v>
+        <v>4.9401</v>
       </c>
       <c r="N2" t="n">
         <v>208</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3733</v>
+        <v>5.2956</v>
       </c>
       <c r="C3" t="n">
-        <v>1.738</v>
+        <v>1.7128</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6968</v>
+        <v>1.7527</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3733</v>
+        <v>5.2956</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7554</v>
+        <v>2.2915</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6179</v>
+        <v>3.0041</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7554</v>
+        <v>2.5875</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0438</v>
+        <v>1.3454</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6179</v>
+        <v>3.0041</v>
       </c>
       <c r="K3" t="n">
         <v>44</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6617</v>
+        <v>4.3495</v>
       </c>
       <c r="N3" t="n">
         <v>166</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2327</v>
+        <v>4.4642</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6925</v>
+        <v>1.4439</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6408</v>
+        <v>1.3773</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2327</v>
+        <v>4.4642</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6069</v>
+        <v>3.0279</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6258</v>
+        <v>1.4363</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6069</v>
+        <v>5.182</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3024</v>
+        <v>2.6944</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6258</v>
+        <v>1.4363</v>
       </c>
       <c r="K4" t="n">
         <v>44</v>
@@ -621,7 +621,7 @@
         <v>122</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9282</v>
+        <v>4.1307</v>
       </c>
       <c r="N4" t="n">
         <v>166</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2062</v>
+        <v>4.4551</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3605</v>
+        <v>1.441</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2318</v>
+        <v>1.3732</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2062</v>
+        <v>4.4551</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7953</v>
+        <v>2.4019</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4109</v>
+        <v>2.0532</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7953</v>
+        <v>2.9766</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4551</v>
+        <v>1.5477</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4109</v>
+        <v>2.0532</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>3.866</v>
+        <v>3.6009</v>
       </c>
       <c r="N5" t="n">
         <v>166</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9203</v>
+        <v>4.2971</v>
       </c>
       <c r="C6" t="n">
-        <v>1.268</v>
+        <v>1.3899</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1179</v>
+        <v>1.3019</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9203</v>
+        <v>4.2971</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6478</v>
+        <v>2.2043</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2725</v>
+        <v>2.0928</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6478</v>
+        <v>2.2803</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3356</v>
+        <v>1.1856</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2725</v>
+        <v>2.0928</v>
       </c>
       <c r="K6" t="n">
         <v>51</v>
@@ -713,7 +713,7 @@
         <v>157</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6081</v>
+        <v>3.2784</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5235</v>
+        <v>3.6827</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1397</v>
+        <v>1.1912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9599</v>
+        <v>1.0245</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5235</v>
+        <v>3.6827</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1206</v>
+        <v>1.4497</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4029</v>
+        <v>2.233</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1206</v>
+        <v>1.4497</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9083</v>
+        <v>0.7538</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4029</v>
+        <v>2.233</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3112</v>
+        <v>2.9868</v>
       </c>
       <c r="N7" t="n">
         <v>208</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.625</v>
+        <v>3.2119</v>
       </c>
       <c r="C8" t="n">
-        <v>0.849</v>
+        <v>1.0389</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6019</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.625</v>
+        <v>3.2119</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1993</v>
+        <v>2.0413</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4257</v>
+        <v>1.1706</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1993</v>
+        <v>2.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9721</v>
+        <v>1.0614</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4257</v>
+        <v>1.1706</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3978</v>
+        <v>2.232</v>
       </c>
       <c r="N8" t="n">
         <v>166</v>
@@ -814,81 +814,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0184</v>
+        <v>3.055</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6528</v>
+        <v>0.9881</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3602</v>
+        <v>0.7412</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0184</v>
+        <v>3.055</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0184</v>
+        <v>2.2137</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.8413</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0184</v>
+        <v>2.3133</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0184</v>
+        <v>1.2028</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8413</v>
       </c>
       <c r="K9" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0184</v>
+        <v>2.0441</v>
       </c>
       <c r="N9" t="n">
-        <v>83</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9661</v>
+        <v>2.7244</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6359</v>
+        <v>0.8812</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3394</v>
+        <v>0.5919</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9661</v>
+        <v>2.7244</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3571</v>
+        <v>2.2024</v>
       </c>
       <c r="G10" t="n">
-        <v>0.609</v>
+        <v>0.522</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3571</v>
+        <v>2.2735</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.1821</v>
       </c>
       <c r="J10" t="n">
-        <v>0.609</v>
+        <v>0.522</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>1.709</v>
+        <v>1.7041</v>
       </c>
       <c r="N10" t="n">
         <v>208</v>
@@ -906,78 +906,78 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7089</v>
+        <v>2.4016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5527</v>
+        <v>0.7768</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2369</v>
+        <v>0.4462</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7089</v>
+        <v>2.4016</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2672</v>
+        <v>1.9838</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4417</v>
+        <v>0.4178</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2672</v>
+        <v>1.9838</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0271</v>
+        <v>1.0315</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4417</v>
+        <v>0.4178</v>
       </c>
       <c r="K11" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L11" t="n">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4688</v>
+        <v>1.4493</v>
       </c>
       <c r="N11" t="n">
-        <v>208</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4858</v>
+        <v>0.7454</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1545</v>
+        <v>0.4024</v>
       </c>
       <c r="E12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="F12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="I12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.502</v>
+        <v>2.3046</v>
       </c>
       <c r="N12" t="n">
         <v>83</v>
@@ -998,124 +998,124 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4502</v>
+        <v>1.6954</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4691</v>
+        <v>0.5484</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1338</v>
+        <v>0.1274</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4502</v>
+        <v>1.6954</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1374</v>
+        <v>2.3728</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3128</v>
+        <v>-0.6774</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1374</v>
+        <v>2.8739</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9219000000000001</v>
+        <v>1.4943</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3128</v>
+        <v>-0.6774</v>
       </c>
       <c r="K13" t="n">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2347</v>
+        <v>0.8169</v>
       </c>
       <c r="N13" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3945</v>
+        <v>1.5896</v>
       </c>
       <c r="C14" t="n">
-        <v>0.451</v>
+        <v>0.5142</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1117</v>
+        <v>0.0796</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3945</v>
+        <v>1.5896</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3945</v>
+        <v>1.6192</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0296</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3945</v>
+        <v>1.6192</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3945</v>
+        <v>0.8419</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0296</v>
       </c>
       <c r="K14" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3945</v>
+        <v>0.8123</v>
       </c>
       <c r="N14" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2958</v>
+        <v>0.4801</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0795</v>
+        <v>0.0321</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9146</v>
+        <v>1.4844</v>
       </c>
       <c r="N15" t="n">
         <v>78</v>
@@ -1136,170 +1136,170 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2727</v>
+        <v>0.4778</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1081</v>
+        <v>0.0289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="F16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="I16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.843</v>
+        <v>1.4772</v>
       </c>
       <c r="N16" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8322000000000001</v>
+        <v>1.2372</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2692</v>
+        <v>0.4002</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1124</v>
+        <v>-0.0795</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8322000000000001</v>
+        <v>1.2372</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8577</v>
+        <v>1.9129</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0255</v>
+        <v>-0.6757</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8577</v>
+        <v>1.9129</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6952</v>
+        <v>0.9946</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0255</v>
+        <v>-0.6757</v>
       </c>
       <c r="K17" t="n">
         <v>83</v>
       </c>
       <c r="L17" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6697000000000001</v>
+        <v>0.3189000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.527</v>
+        <v>1.0067</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1705</v>
+        <v>0.3256</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.234</v>
+        <v>-0.1835</v>
       </c>
       <c r="E18" t="n">
-        <v>0.527</v>
+        <v>1.0067</v>
       </c>
       <c r="F18" t="n">
-        <v>1.527</v>
+        <v>1.0067</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.527</v>
+        <v>1.0067</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2377</v>
+        <v>1.0067</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="L18" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2377</v>
+        <v>1.0067</v>
       </c>
       <c r="N18" t="n">
-        <v>182</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1078</v>
+        <v>0.3037</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3112</v>
+        <v>-0.2142</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3332</v>
+        <v>0.9388</v>
       </c>
       <c r="N19" t="n">
         <v>78</v>
@@ -1320,81 +1320,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0694</v>
+        <v>0.1715</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3584</v>
+        <v>-0.3987</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2146</v>
+        <v>0.5301</v>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2077</v>
+        <v>0.4224</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0672</v>
+        <v>0.1366</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3612</v>
+        <v>-0.4473</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2077</v>
+        <v>0.4224</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1655</v>
+        <v>0.8195</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9578</v>
+        <v>-0.3971</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1655</v>
+        <v>0.8195</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9447</v>
+        <v>0.4261</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9578</v>
+        <v>-0.3971</v>
       </c>
       <c r="K21" t="n">
         <v>83</v>
@@ -1403,7 +1403,7 @@
         <v>83</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0131</v>
+        <v>0.02899999999999997</v>
       </c>
       <c r="N21" t="n">
         <v>166</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.1028</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4332</v>
+        <v>-0.4945</v>
       </c>
       <c r="E22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="F22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="I22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.027</v>
+        <v>0.3178</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1458,262 +1458,262 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0334</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4851</v>
+        <v>-0.5023</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1033</v>
+        <v>0.3006</v>
       </c>
       <c r="N23" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1097</v>
+        <v>0.2513</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0355</v>
+        <v>0.0813</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4876</v>
+        <v>-0.5246</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1097</v>
+        <v>0.2513</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1097</v>
+        <v>1.1264</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.8751</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1097</v>
+        <v>1.1264</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1097</v>
+        <v>0.5857</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.8751</v>
       </c>
       <c r="K24" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1097</v>
+        <v>-0.2894</v>
       </c>
       <c r="N24" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0419</v>
+        <v>0.0547</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4955</v>
+        <v>-0.5616</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1296</v>
+        <v>0.1692</v>
       </c>
       <c r="N25" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0453</v>
+        <v>-0.0211</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4998</v>
+        <v>-0.6674</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1402</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2495</v>
+        <v>-0.1254</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0406</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5433</v>
+        <v>-0.6946</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2495</v>
+        <v>-0.1254</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3135</v>
+        <v>-0.1254</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3135</v>
+        <v>-0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2541</v>
+        <v>-0.1254</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L27" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3089</v>
+        <v>-0.1254</v>
       </c>
       <c r="N27" t="n">
-        <v>166</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1309</v>
+        <v>-0.0442</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6052</v>
+        <v>-0.6996</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4048</v>
+        <v>-0.1365</v>
       </c>
       <c r="N28" t="n">
         <v>51</v>
@@ -1734,124 +1734,124 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5536</v>
+        <v>-0.2712</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1791</v>
+        <v>-0.0877</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6645</v>
+        <v>-0.7604</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5536</v>
+        <v>-0.2712</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5536</v>
+        <v>0.8403</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1.1115</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5536</v>
+        <v>0.8403</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5536</v>
+        <v>0.4369</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1.1115</v>
       </c>
       <c r="K29" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5536</v>
+        <v>-0.6745999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5626</v>
+        <v>-0.3145</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.182</v>
+        <v>-0.1017</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6681</v>
+        <v>-0.78</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5626</v>
+        <v>-0.3145</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4374</v>
+        <v>-0.3145</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4374</v>
+        <v>-0.3145</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3545</v>
+        <v>-0.3145</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L30" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6455</v>
+        <v>-0.3145</v>
       </c>
       <c r="N30" t="n">
-        <v>166</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2948</v>
+        <v>-0.1112</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.7932</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9114</v>
+        <v>-0.3437</v>
       </c>
       <c r="N31" t="n">
         <v>49</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9643</v>
+        <v>-0.6443</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3119</v>
+        <v>-0.2084</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9643</v>
+        <v>-0.6443</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5942</v>
+        <v>-0.6443</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3701</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5942</v>
+        <v>-0.6443</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4816</v>
+        <v>-0.6443</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3701</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L32" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8516999999999999</v>
+        <v>-0.6443</v>
       </c>
       <c r="N32" t="n">
-        <v>166</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>pancc</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0744</v>
+        <v>-0.7405</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3475</v>
+        <v>-0.2395</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.872</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0744</v>
+        <v>-0.7405</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3532</v>
+        <v>-0.7405</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7212</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3532</v>
+        <v>-0.7405</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2863</v>
+        <v>-0.7405</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7212</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L33" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0075</v>
+        <v>-0.7405</v>
       </c>
       <c r="N33" t="n">
-        <v>131</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3539</v>
+        <v>-0.2466</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8798</v>
+        <v>-0.9822</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.094</v>
+        <v>-0.7624</v>
       </c>
       <c r="N34" t="n">
         <v>83</v>
@@ -2010,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pancc</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1191</v>
+        <v>-0.768</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.362</v>
+        <v>-0.2484</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8898</v>
+        <v>-0.9847</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1191</v>
+        <v>-0.768</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1191</v>
+        <v>-0.2329</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.5351</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1191</v>
+        <v>-0.2329</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1191</v>
+        <v>-0.1211</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.5351</v>
       </c>
       <c r="K35" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1191</v>
+        <v>-0.6562</v>
       </c>
       <c r="N35" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.203</v>
+        <v>-0.8138</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3891</v>
+        <v>-0.2632</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9232</v>
+        <v>-1.0054</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.203</v>
+        <v>-0.8138</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4139</v>
+        <v>-0.5668</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7891</v>
+        <v>-0.247</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4139</v>
+        <v>-0.5668</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3355</v>
+        <v>-0.2947</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7891</v>
+        <v>-0.247</v>
       </c>
       <c r="K36" t="n">
         <v>83</v>
       </c>
       <c r="L36" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1246</v>
+        <v>-0.5417000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2739</v>
+        <v>-0.8381</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.412</v>
+        <v>-0.2711</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9514</v>
+        <v>-1.0164</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2739</v>
+        <v>-0.8381</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2739</v>
+        <v>-0.3204</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5177</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2739</v>
+        <v>-0.3204</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2739</v>
+        <v>-0.1666</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5177</v>
       </c>
       <c r="K37" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2739</v>
+        <v>-0.6843</v>
       </c>
       <c r="N37" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2799</v>
+        <v>-0.8699</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.414</v>
+        <v>-0.2814</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9538</v>
+        <v>-1.0307</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2799</v>
+        <v>-0.8699</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3109</v>
+        <v>-0.8699</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.5908</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3109</v>
+        <v>-0.8699</v>
       </c>
       <c r="I38" t="n">
-        <v>0.252</v>
+        <v>-0.8699</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.5908</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L38" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3388</v>
+        <v>-0.8699</v>
       </c>
       <c r="N38" t="n">
-        <v>166</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4706</v>
+        <v>-0.3175</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0236</v>
+        <v>-1.0812</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4551</v>
+        <v>-0.9816</v>
       </c>
       <c r="N39" t="n">
         <v>78</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3594</v>
+        <v>-2.9137</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7631</v>
+        <v>-0.9424</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3839</v>
+        <v>-1.9534</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3594</v>
+        <v>-2.9137</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.1497</v>
+        <v>-2.8864</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2097</v>
+        <v>-0.0273</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.1497</v>
+        <v>-2.8864</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7424</v>
+        <v>-1.5008</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2097</v>
+        <v>-0.0273</v>
       </c>
       <c r="K40" t="n">
         <v>83</v>
@@ -2277,7 +2277,7 @@
         <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9521</v>
+        <v>-1.5281</v>
       </c>
       <c r="N40" t="n">
         <v>131</v>
@@ -2383,10 +2383,10 @@
         <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2748</v>
+        <v>0.215</v>
       </c>
       <c r="J2" t="n">
-        <v>5.496</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>0.74</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3827</v>
+        <v>-0.2665</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.654</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>0.73</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4006</v>
+        <v>-0.2757</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.012</v>
+        <v>-5.514</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5667</v>
+        <v>-0.3788</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.334</v>
+        <v>-7.576</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5942</v>
+        <v>-0.3975</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.884</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0713</v>
+        <v>0.9845</v>
       </c>
       <c r="J7" t="n">
-        <v>21.426</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8369</v>
+        <v>0.768</v>
       </c>
       <c r="J8" t="n">
-        <v>16.738</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4958</v>
       </c>
       <c r="J9" t="n">
-        <v>10.09</v>
+        <v>9.916</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2172</v>
+        <v>0.2441</v>
       </c>
       <c r="J10" t="n">
-        <v>4.344</v>
+        <v>4.882</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.014</v>
+        <v>0.0318</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.28</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3045</v>
+        <v>1.1965</v>
       </c>
       <c r="J12" t="n">
-        <v>35.2215</v>
+        <v>32.3055</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5787</v>
+        <v>0.6256</v>
       </c>
       <c r="J13" t="n">
-        <v>15.6249</v>
+        <v>16.8912</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J14" t="n">
-        <v>14.8122</v>
+        <v>16.2675</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4124</v>
+        <v>0.4809</v>
       </c>
       <c r="J15" t="n">
-        <v>11.1348</v>
+        <v>12.9843</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1353</v>
+        <v>-0.0571</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.6531</v>
+        <v>-1.5417</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.14</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3295</v>
+        <v>0.3588</v>
       </c>
       <c r="J17" t="n">
-        <v>8.8965</v>
+        <v>9.6876</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0264</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2268</v>
+        <v>-0.7128</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.182</v>
+        <v>-0.1244</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.914</v>
+        <v>-3.3588</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>0.86</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2592</v>
+        <v>-0.1662</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.9984</v>
+        <v>-4.4874</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5919</v>
+        <v>-0.3904</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.9813</v>
+        <v>-10.5408</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9361</v>
+        <v>0.9333</v>
       </c>
       <c r="J22" t="n">
-        <v>25.2747</v>
+        <v>25.1991</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7039</v>
+        <v>0.7043</v>
       </c>
       <c r="J23" t="n">
-        <v>19.0053</v>
+        <v>19.0161</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5738</v>
+        <v>0.5859</v>
       </c>
       <c r="J24" t="n">
-        <v>15.4926</v>
+        <v>15.8193</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5142</v>
+        <v>0.5382</v>
       </c>
       <c r="J25" t="n">
-        <v>13.8834</v>
+        <v>14.5314</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.444</v>
+        <v>-0.3707</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.988</v>
+        <v>-10.0089</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2336</v>
+        <v>0.2312</v>
       </c>
       <c r="J27" t="n">
-        <v>6.3072</v>
+        <v>6.2424</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1637</v>
+        <v>-0.1302</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.4199</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1822</v>
+        <v>-0.141</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.9194</v>
+        <v>-3.807</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4719</v>
+        <v>-0.308</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.7413</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4859</v>
+        <v>-0.3175</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.1193</v>
+        <v>-8.5725</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>2.01</v>
       </c>
       <c r="I32" t="n">
-        <v>1.868</v>
+        <v>1.388</v>
       </c>
       <c r="J32" t="n">
-        <v>33.624</v>
+        <v>24.984</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>1.5011</v>
+        <v>1.0769</v>
       </c>
       <c r="J33" t="n">
-        <v>27.0198</v>
+        <v>19.3842</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>1.56</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1559</v>
+        <v>0.8847</v>
       </c>
       <c r="J34" t="n">
-        <v>20.8062</v>
+        <v>15.9246</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.701</v>
+        <v>0.6301</v>
       </c>
       <c r="J35" t="n">
-        <v>12.618</v>
+        <v>11.3418</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>1.14</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2281</v>
+        <v>0.3308</v>
       </c>
       <c r="J36" t="n">
-        <v>4.1058</v>
+        <v>5.9544</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1178</v>
+        <v>-0.1214</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.1204</v>
+        <v>-2.1852</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3968</v>
+        <v>-0.3194</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.1424</v>
+        <v>-5.7492</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>0.55</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5788</v>
+        <v>-0.4122</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.4184</v>
+        <v>-7.4196</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7487</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.4766</v>
+        <v>-9.2628</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.35</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8697</v>
+        <v>-0.6015</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.6546</v>
+        <v>-10.827</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8516</v>
+        <v>0.6259</v>
       </c>
       <c r="J42" t="n">
-        <v>25.548</v>
+        <v>18.777</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7584</v>
+        <v>0.5692</v>
       </c>
       <c r="J43" t="n">
-        <v>22.752</v>
+        <v>17.076</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5845</v>
+        <v>0.467</v>
       </c>
       <c r="J44" t="n">
-        <v>17.535</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2181</v>
+        <v>-0.1543</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.543</v>
+        <v>-4.629</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8189</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.567</v>
+        <v>-23.271</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3691</v>
+        <v>0.3849</v>
       </c>
       <c r="J47" t="n">
-        <v>11.073</v>
+        <v>11.547</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.03</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>2.769</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0404</v>
+        <v>-0.0205</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.212</v>
+        <v>-0.615</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1354</v>
+        <v>-0.0759</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.062</v>
+        <v>-2.277</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3244</v>
+        <v>-0.1983</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.731999999999999</v>
+        <v>-5.949</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>2.07</v>
       </c>
       <c r="I52" t="n">
-        <v>1.9513</v>
+        <v>1.4868</v>
       </c>
       <c r="J52" t="n">
-        <v>42.9286</v>
+        <v>32.7096</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.57</v>
       </c>
       <c r="I53" t="n">
-        <v>1.2557</v>
+        <v>0.9112</v>
       </c>
       <c r="J53" t="n">
-        <v>27.6254</v>
+        <v>20.0464</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>1.36</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7766</v>
+        <v>0.6581</v>
       </c>
       <c r="J54" t="n">
-        <v>17.0852</v>
+        <v>14.4782</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>1.25</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5263</v>
+        <v>0.512</v>
       </c>
       <c r="J55" t="n">
-        <v>11.5786</v>
+        <v>11.264</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.86</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6313</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.8886</v>
+        <v>-12.408</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>0.85</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1634</v>
+        <v>-0.1485</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.5948</v>
+        <v>-3.267</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.277</v>
+        <v>-0.2228</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.094</v>
+        <v>-4.9016</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2933</v>
+        <v>-0.2328</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.4526</v>
+        <v>-5.1216</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.608</v>
+        <v>-0.4096</v>
       </c>
       <c r="J60" t="n">
-        <v>-13.376</v>
+        <v>-9.011200000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6217</v>
+        <v>-0.4189</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.6774</v>
+        <v>-9.2158</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4413</v>
+        <v>0.3684</v>
       </c>
       <c r="J62" t="n">
-        <v>15.8868</v>
+        <v>13.2624</v>
       </c>
     </row>
     <row r="63">
@@ -4823,10 +4823,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3258</v>
+        <v>0.2795</v>
       </c>
       <c r="J63" t="n">
-        <v>11.7288</v>
+        <v>10.062</v>
       </c>
     </row>
     <row r="64">
@@ -4863,10 +4863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1537</v>
+        <v>-0.0877</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.5332</v>
+        <v>-3.1572</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>0.93</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1729</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.2244</v>
+        <v>-3.5856</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.71</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5064</v>
+        <v>-0.3263</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.2304</v>
+        <v>-11.7468</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5437</v>
+        <v>0.4107</v>
       </c>
       <c r="J67" t="n">
-        <v>19.5732</v>
+        <v>14.7852</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3078</v>
+        <v>0.2504</v>
       </c>
       <c r="J68" t="n">
-        <v>11.0808</v>
+        <v>9.0144</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0346</v>
+        <v>0.043</v>
       </c>
       <c r="J69" t="n">
-        <v>1.2456</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1892</v>
+        <v>-0.1049</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.8112</v>
+        <v>-3.7764</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4077</v>
+        <v>-0.2542</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.6772</v>
+        <v>-9.151199999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6984</v>
+        <v>1.1908</v>
       </c>
       <c r="J72" t="n">
-        <v>42.46</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.66</v>
       </c>
       <c r="I73" t="n">
-        <v>1.4705</v>
+        <v>1.0362</v>
       </c>
       <c r="J73" t="n">
-        <v>36.7625</v>
+        <v>25.905</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8542</v>
+        <v>0.6661</v>
       </c>
       <c r="J74" t="n">
-        <v>21.355</v>
+        <v>16.6525</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2989</v>
+        <v>-0.2125</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.4725</v>
+        <v>-5.3125</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6131</v>
+        <v>-0.5452</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.3275</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.613</v>
+        <v>0.577</v>
       </c>
       <c r="J77" t="n">
-        <v>15.325</v>
+        <v>14.425</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2568</v>
+        <v>-0.1887</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.42</v>
+        <v>-4.7175</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3206</v>
+        <v>-0.2173</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.015000000000001</v>
+        <v>-5.4325</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5326</v>
+        <v>-0.3513</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.315</v>
+        <v>-8.782500000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.49</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7504</v>
+        <v>-0.5092</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.76</v>
+        <v>-12.73</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.989</v>
+        <v>0.9646</v>
       </c>
       <c r="J82" t="n">
-        <v>28.681</v>
+        <v>27.9734</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3314</v>
+        <v>0.3054</v>
       </c>
       <c r="J83" t="n">
-        <v>9.6106</v>
+        <v>8.8566</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1887</v>
+        <v>0.1865</v>
       </c>
       <c r="J84" t="n">
-        <v>5.4723</v>
+        <v>5.4085</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.99</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1099</v>
+        <v>-0.0643</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.1871</v>
+        <v>-1.8647</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.76</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7819</v>
+        <v>-0.7379</v>
       </c>
       <c r="J86" t="n">
-        <v>-22.6751</v>
+        <v>-21.3991</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3906</v>
+        <v>0.4453</v>
       </c>
       <c r="J87" t="n">
-        <v>11.3274</v>
+        <v>12.9137</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3007</v>
+        <v>0.3315</v>
       </c>
       <c r="J88" t="n">
-        <v>8.7203</v>
+        <v>9.6135</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.147</v>
+        <v>-0.0861</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.263</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.319</v>
+        <v>-0.196</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.250999999999999</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4075</v>
+        <v>-0.2566</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.8175</v>
+        <v>-7.4414</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>0.98</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0396</v>
+        <v>-0.0051</v>
       </c>
       <c r="J92" t="n">
-        <v>0.9504</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>0.82</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.255</v>
+        <v>-0.1953</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.12</v>
+        <v>-4.6872</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.273</v>
+        <v>-0.2052</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.552</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.355</v>
+        <v>-0.2427</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.52</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6443</v>
+        <v>-0.4312</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.4632</v>
+        <v>-10.3488</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4838</v>
+        <v>1.3146</v>
       </c>
       <c r="J97" t="n">
-        <v>35.6112</v>
+        <v>31.5504</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7047</v>
+        <v>0.7347</v>
       </c>
       <c r="J98" t="n">
-        <v>16.9128</v>
+        <v>17.6328</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5569</v>
+        <v>0.6219</v>
       </c>
       <c r="J99" t="n">
-        <v>13.3656</v>
+        <v>14.9256</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.21</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5041</v>
+        <v>0.5745</v>
       </c>
       <c r="J100" t="n">
-        <v>12.0984</v>
+        <v>13.788</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4364</v>
+        <v>-0.3585</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.4736</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2901</v>
+        <v>0.3162</v>
       </c>
       <c r="J102" t="n">
-        <v>8.702999999999999</v>
+        <v>9.486000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1694</v>
+        <v>0.1697</v>
       </c>
       <c r="J103" t="n">
-        <v>5.082</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0131</v>
+        <v>-0.0182</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.393</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0131</v>
+        <v>-0.0182</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.393</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5657</v>
+        <v>-0.37</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.971</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8964</v>
+        <v>0.8838</v>
       </c>
       <c r="J107" t="n">
-        <v>26.892</v>
+        <v>26.514</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8511</v>
+        <v>0.8371</v>
       </c>
       <c r="J108" t="n">
-        <v>25.533</v>
+        <v>25.113</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4095</v>
+        <v>0.4224</v>
       </c>
       <c r="J109" t="n">
-        <v>12.285</v>
+        <v>12.672</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2738</v>
+        <v>0.3169</v>
       </c>
       <c r="J110" t="n">
-        <v>8.214</v>
+        <v>9.507</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.6593</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.396</v>
+        <v>-19.779</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.6243</v>
+        <v>1.4115</v>
       </c>
       <c r="J112" t="n">
-        <v>38.9832</v>
+        <v>33.876</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>1.72</v>
       </c>
       <c r="I113" t="n">
-        <v>1.5702</v>
+        <v>1.3761</v>
       </c>
       <c r="J113" t="n">
-        <v>37.6848</v>
+        <v>33.0264</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.6032</v>
       </c>
       <c r="J114" t="n">
-        <v>12.1584</v>
+        <v>14.4768</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2578</v>
+        <v>0.3502</v>
       </c>
       <c r="J115" t="n">
-        <v>6.1872</v>
+        <v>8.4048</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4309</v>
+        <v>-0.3493</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.3416</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4021</v>
+        <v>0.4516</v>
       </c>
       <c r="J117" t="n">
-        <v>9.650399999999999</v>
+        <v>10.8384</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1544</v>
+        <v>-0.1331</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.7056</v>
+        <v>-3.1944</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4077</v>
+        <v>-0.2719</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.784800000000001</v>
+        <v>-6.5256</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>0.66</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5254</v>
+        <v>-0.3478</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.6096</v>
+        <v>-8.347200000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.54</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.4599</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.416</v>
+        <v>-11.0376</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4253</v>
+        <v>0.4887</v>
       </c>
       <c r="J122" t="n">
-        <v>12.759</v>
+        <v>14.661</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1313</v>
+        <v>0.1243</v>
       </c>
       <c r="J123" t="n">
-        <v>3.939</v>
+        <v>3.729</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0109</v>
+        <v>-0.0178</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.327</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2821</v>
+        <v>-0.1731</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.462999999999999</v>
+        <v>-5.193</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.513</v>
+        <v>-0.3319</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.39</v>
+        <v>-9.957000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6964</v>
+        <v>0.6662</v>
       </c>
       <c r="J127" t="n">
-        <v>20.892</v>
+        <v>19.986</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.12</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4022</v>
+        <v>0.3819</v>
       </c>
       <c r="J128" t="n">
-        <v>12.066</v>
+        <v>11.457</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2265</v>
+        <v>0.2427</v>
       </c>
       <c r="J129" t="n">
-        <v>6.795</v>
+        <v>7.281</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.153</v>
+        <v>0.1819</v>
       </c>
       <c r="J130" t="n">
-        <v>4.59</v>
+        <v>5.457</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4038</v>
+        <v>-0.3413</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.114</v>
+        <v>-10.239</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.79</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0709</v>
+        <v>1.2374</v>
       </c>
       <c r="J132" t="n">
-        <v>32.127</v>
+        <v>37.122</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>0.89</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2501</v>
+        <v>-0.1473</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.503</v>
+        <v>-4.419</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2825</v>
+        <v>-0.1689</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.475</v>
+        <v>-5.067</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3587</v>
+        <v>-0.2209</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.761</v>
+        <v>-6.627</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4973</v>
+        <v>-0.3192</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.919</v>
+        <v>-9.576000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1905</v>
+        <v>1.1153</v>
       </c>
       <c r="J137" t="n">
-        <v>35.715</v>
+        <v>33.459</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6041</v>
+        <v>0.5819</v>
       </c>
       <c r="J138" t="n">
-        <v>18.123</v>
+        <v>17.457</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.022</v>
+        <v>0.0308</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.66</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.245</v>
+        <v>-2.361</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5528</v>
+        <v>-0.491</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.584</v>
+        <v>-14.73</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.353</v>
+        <v>1.2267</v>
       </c>
       <c r="J142" t="n">
-        <v>33.825</v>
+        <v>30.6675</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9651</v>
+        <v>0.9655</v>
       </c>
       <c r="J143" t="n">
-        <v>24.1275</v>
+        <v>24.1375</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4245</v>
+        <v>0.485</v>
       </c>
       <c r="J144" t="n">
-        <v>10.6125</v>
+        <v>12.125</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1407</v>
+        <v>0.2115</v>
       </c>
       <c r="J145" t="n">
-        <v>3.5175</v>
+        <v>5.2875</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5342</v>
+        <v>-0.464</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.355</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4769</v>
+        <v>0.5535</v>
       </c>
       <c r="J147" t="n">
-        <v>11.9225</v>
+        <v>13.8375</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1318</v>
+        <v>-0.1093</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.295</v>
+        <v>-2.7325</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2728</v>
+        <v>-0.1822</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.82</v>
+        <v>-4.555</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5163</v>
+        <v>-0.3379</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.9075</v>
+        <v>-8.4475</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5698</v>
+        <v>-0.3756</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.245</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4293</v>
+        <v>0.489</v>
       </c>
       <c r="J152" t="n">
-        <v>9.873900000000001</v>
+        <v>11.247</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3087</v>
+        <v>0.3295</v>
       </c>
       <c r="J153" t="n">
-        <v>7.1001</v>
+        <v>7.5785</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4219</v>
+        <v>-0.2727</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.7037</v>
+        <v>-6.2721</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4648</v>
+        <v>-0.3016</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.6904</v>
+        <v>-6.9368</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6496</v>
+        <v>-0.4333</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.9408</v>
+        <v>-9.9659</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.018</v>
+        <v>1.0192</v>
       </c>
       <c r="J157" t="n">
-        <v>23.414</v>
+        <v>23.4416</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9307</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>21.4061</v>
+        <v>21.8293</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>1.35</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8626</v>
+        <v>0.8862</v>
       </c>
       <c r="J159" t="n">
-        <v>19.8398</v>
+        <v>20.3826</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>1.28</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6847</v>
+        <v>0.7319</v>
       </c>
       <c r="J160" t="n">
-        <v>15.7481</v>
+        <v>16.8337</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3196</v>
+        <v>-0.236</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.3508</v>
+        <v>-5.428</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.84</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8357</v>
+        <v>1.5518</v>
       </c>
       <c r="J162" t="n">
-        <v>49.5639</v>
+        <v>41.8986</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8526</v>
       </c>
       <c r="J163" t="n">
-        <v>22.7394</v>
+        <v>23.0202</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5205</v>
+        <v>0.5789</v>
       </c>
       <c r="J164" t="n">
-        <v>14.0535</v>
+        <v>15.6303</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.98</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2351</v>
+        <v>-0.1532</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.3477</v>
+        <v>-4.1364</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6572</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.2834</v>
+        <v>-17.7444</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1517</v>
+        <v>0.1302</v>
       </c>
       <c r="J167" t="n">
-        <v>4.0959</v>
+        <v>3.5154</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>0.91</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1318</v>
+        <v>-0.1093</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.5586</v>
+        <v>-2.9511</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1692</v>
+        <v>-0.1314</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.5684</v>
+        <v>-3.5478</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4025</v>
+        <v>-0.2611</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.8675</v>
+        <v>-7.0497</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.71</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4748</v>
+        <v>-0.3093</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8196</v>
+        <v>-8.351100000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.7079</v>
+        <v>1.4717</v>
       </c>
       <c r="J172" t="n">
-        <v>32.4501</v>
+        <v>27.9623</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1617</v>
+        <v>1.1339</v>
       </c>
       <c r="J173" t="n">
-        <v>22.0723</v>
+        <v>21.5441</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.47</v>
       </c>
       <c r="I174" t="n">
-        <v>1.0306</v>
+        <v>1.0627</v>
       </c>
       <c r="J174" t="n">
-        <v>19.5814</v>
+        <v>20.1913</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7862</v>
+        <v>0.9009</v>
       </c>
       <c r="J175" t="n">
-        <v>14.9378</v>
+        <v>17.1171</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.007</v>
+        <v>0.0959</v>
       </c>
       <c r="J176" t="n">
-        <v>0.133</v>
+        <v>1.8221</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>0.86</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0988</v>
+        <v>-0.1076</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.8772</v>
+        <v>-2.0444</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>0.79</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2107</v>
+        <v>-0.1881</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.0033</v>
+        <v>-3.5739</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3984</v>
+        <v>-0.3124</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.5696</v>
+        <v>-5.9356</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6849</v>
+        <v>-0.468</v>
       </c>
       <c r="J180" t="n">
-        <v>-13.0131</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.26</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9918</v>
+        <v>-0.6968</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.8442</v>
+        <v>-13.2392</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4290/event_4290_evp_summary.xlsx
+++ b/database/event/4290/event_4290_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9418</v>
+        <v>5.9952</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9219</v>
+        <v>1.9391</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0444</v>
+        <v>2.1049</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9418</v>
+        <v>5.9952</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2246</v>
+        <v>2.1681</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7172</v>
+        <v>3.827</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3519</v>
+        <v>2.2593</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2229</v>
+        <v>1.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7172</v>
+        <v>3.827</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9401</v>
+        <v>5.047</v>
       </c>
       <c r="N2" t="n">
         <v>208</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2956</v>
+        <v>5.396</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7128</v>
+        <v>1.7453</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7527</v>
+        <v>1.8322</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2956</v>
+        <v>5.396</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2915</v>
+        <v>2.2307</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0041</v>
+        <v>3.1653</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5875</v>
+        <v>2.4656</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3454</v>
+        <v>1.3314</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0041</v>
+        <v>3.1653</v>
       </c>
       <c r="K3" t="n">
         <v>44</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3495</v>
+        <v>4.4967</v>
       </c>
       <c r="N3" t="n">
         <v>166</v>
@@ -584,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4642</v>
+        <v>4.5343</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4439</v>
+        <v>1.4666</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3773</v>
+        <v>1.4399</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4642</v>
+        <v>4.5343</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0279</v>
+        <v>2.1672</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4363</v>
+        <v>2.3671</v>
       </c>
       <c r="H4" t="n">
-        <v>5.182</v>
+        <v>2.2561</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6944</v>
+        <v>1.2183</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4363</v>
+        <v>2.3671</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1307</v>
+        <v>3.5854</v>
       </c>
       <c r="N4" t="n">
-        <v>166</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4551</v>
+        <v>4.5279</v>
       </c>
       <c r="C5" t="n">
-        <v>1.441</v>
+        <v>1.4645</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3732</v>
+        <v>1.437</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4551</v>
+        <v>4.5279</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4019</v>
+        <v>2.9773</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0532</v>
+        <v>1.5506</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9766</v>
+        <v>4.929</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5477</v>
+        <v>2.6616</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0532</v>
+        <v>1.5506</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6009</v>
+        <v>4.2122</v>
       </c>
       <c r="N5" t="n">
         <v>166</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2971</v>
+        <v>4.504</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3899</v>
+        <v>1.4568</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3019</v>
+        <v>1.4261</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2971</v>
+        <v>4.504</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2043</v>
+        <v>2.3268</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0928</v>
+        <v>2.1772</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2803</v>
+        <v>2.7828</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1856</v>
+        <v>1.5027</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0928</v>
+        <v>2.1772</v>
       </c>
       <c r="K6" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2784</v>
+        <v>3.6799</v>
       </c>
       <c r="N6" t="n">
-        <v>208</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6827</v>
+        <v>3.8185</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1912</v>
+        <v>1.2351</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0245</v>
+        <v>1.1141</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6827</v>
+        <v>3.8185</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4497</v>
+        <v>1.4637</v>
       </c>
       <c r="G7" t="n">
-        <v>2.233</v>
+        <v>2.3548</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4497</v>
+        <v>1.4637</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7538</v>
+        <v>0.7904</v>
       </c>
       <c r="J7" t="n">
-        <v>2.233</v>
+        <v>2.3548</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9868</v>
+        <v>3.1452</v>
       </c>
       <c r="N7" t="n">
         <v>208</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2119</v>
+        <v>3.2201</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0389</v>
+        <v>1.0415</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8417</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2119</v>
+        <v>3.2201</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0413</v>
+        <v>1.9226</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1706</v>
+        <v>1.2975</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0413</v>
+        <v>1.9226</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0614</v>
+        <v>1.0382</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1706</v>
+        <v>1.2975</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>2.232</v>
+        <v>2.3357</v>
       </c>
       <c r="N8" t="n">
         <v>166</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.055</v>
+        <v>3.0487</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9881</v>
+        <v>0.9861</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7412</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.055</v>
+        <v>3.0487</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2137</v>
+        <v>2.1391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8413</v>
+        <v>0.9096</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3133</v>
+        <v>2.1636</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2028</v>
+        <v>1.1683</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8413</v>
+        <v>0.9096</v>
       </c>
       <c r="K9" t="n">
         <v>51</v>
@@ -851,7 +851,7 @@
         <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0441</v>
+        <v>2.0779</v>
       </c>
       <c r="N9" t="n">
         <v>208</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7244</v>
+        <v>2.631</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8812</v>
+        <v>0.851</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5919</v>
+        <v>0.5735</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7244</v>
+        <v>2.631</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2024</v>
+        <v>2.1306</v>
       </c>
       <c r="G10" t="n">
-        <v>0.522</v>
+        <v>0.5004</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2735</v>
+        <v>2.1356</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1821</v>
+        <v>1.1532</v>
       </c>
       <c r="J10" t="n">
-        <v>0.522</v>
+        <v>0.5004</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7041</v>
+        <v>1.6536</v>
       </c>
       <c r="N10" t="n">
         <v>208</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4016</v>
+        <v>2.2643</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7768</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4462</v>
+        <v>0.4066</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4016</v>
+        <v>2.2643</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9838</v>
+        <v>1.7941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4178</v>
+        <v>0.4702</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9838</v>
+        <v>1.7941</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0315</v>
+        <v>0.9688</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4178</v>
+        <v>0.4702</v>
       </c>
       <c r="K11" t="n">
         <v>83</v>
@@ -943,7 +943,7 @@
         <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4493</v>
+        <v>1.439</v>
       </c>
       <c r="N11" t="n">
         <v>166</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7454</v>
+        <v>0.7308</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4024</v>
+        <v>0.4044</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3046</v>
+        <v>2.2595</v>
       </c>
       <c r="N12" t="n">
         <v>83</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6954</v>
+        <v>1.545</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5484</v>
+        <v>0.4997</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1274</v>
+        <v>0.0791</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6954</v>
+        <v>1.545</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3728</v>
+        <v>2.2385</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6774</v>
+        <v>-0.6935</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8739</v>
+        <v>2.4915</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4943</v>
+        <v>1.3454</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6774</v>
+        <v>-0.6935</v>
       </c>
       <c r="K13" t="n">
         <v>134</v>
@@ -1035,7 +1035,7 @@
         <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8169</v>
+        <v>0.6518999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>182</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5896</v>
+        <v>1.4421</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5142</v>
+        <v>0.4664</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0796</v>
+        <v>0.0323</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5896</v>
+        <v>1.4421</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6192</v>
+        <v>1.4421</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0296</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6192</v>
+        <v>1.4421</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8419</v>
+        <v>1.4421</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0296</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>83</v>
       </c>
       <c r="L14" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8123</v>
+        <v>1.4421</v>
       </c>
       <c r="N14" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4844</v>
+        <v>1.4155</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4801</v>
+        <v>0.4578</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0321</v>
+        <v>0.0202</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4844</v>
+        <v>1.4155</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4844</v>
+        <v>1.4697</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.0542</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4844</v>
+        <v>1.4697</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4844</v>
+        <v>0.7936</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.0542</v>
       </c>
       <c r="K15" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4844</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4778</v>
+        <v>0.453</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0289</v>
+        <v>0.0133</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4772</v>
+        <v>1.4004</v>
       </c>
       <c r="N16" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2372</v>
+        <v>1.1016</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4002</v>
+        <v>0.3563</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0795</v>
+        <v>-0.1227</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2372</v>
+        <v>1.1016</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9129</v>
+        <v>1.8289</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6757</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9129</v>
+        <v>1.8289</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9946</v>
+        <v>0.9876</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6757</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>83</v>
@@ -1219,7 +1219,7 @@
         <v>83</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3189000000000001</v>
+        <v>0.2603000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>166</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3256</v>
+        <v>0.3056</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1835</v>
+        <v>-0.1942</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0067</v>
+        <v>0.9447</v>
       </c>
       <c r="N18" t="n">
         <v>78</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3037</v>
+        <v>0.2891</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2142</v>
+        <v>-0.2174</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9388</v>
+        <v>0.8937</v>
       </c>
       <c r="N19" t="n">
         <v>78</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1715</v>
+        <v>0.1495</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3987</v>
+        <v>-0.4138</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5301</v>
+        <v>0.4621</v>
       </c>
       <c r="N20" t="n">
         <v>78</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4224</v>
+        <v>0.329</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1366</v>
+        <v>0.1064</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4473</v>
+        <v>-0.4744</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4224</v>
+        <v>0.329</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8195</v>
+        <v>0.7572</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3971</v>
+        <v>-0.4282</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8195</v>
+        <v>0.7572</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4261</v>
+        <v>0.4089</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3971</v>
+        <v>-0.4282</v>
       </c>
       <c r="K21" t="n">
         <v>83</v>
@@ -1403,7 +1403,7 @@
         <v>83</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02899999999999997</v>
+        <v>-0.01930000000000004</v>
       </c>
       <c r="N21" t="n">
         <v>166</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1028</v>
+        <v>0.0848</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4945</v>
+        <v>-0.5048</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3178</v>
+        <v>0.2623</v>
       </c>
       <c r="N22" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0839</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5023</v>
+        <v>-0.5061</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3006</v>
+        <v>0.2595</v>
       </c>
       <c r="N23" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2513</v>
+        <v>0.132</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0813</v>
+        <v>0.0427</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5246</v>
+        <v>-0.5641</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2513</v>
+        <v>0.132</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1264</v>
+        <v>0.132</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8751</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1264</v>
+        <v>0.132</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5857</v>
+        <v>0.132</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8751</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>83</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="N24" t="n">
         <v>83</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-0.2894</v>
-      </c>
-      <c r="N24" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1692</v>
+        <v>0.0736</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0547</v>
+        <v>0.0238</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5616</v>
+        <v>-0.5907</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1692</v>
+        <v>0.0736</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1692</v>
+        <v>0.9889</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.9153</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1692</v>
+        <v>0.9889</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1692</v>
+        <v>0.534</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.9153</v>
       </c>
       <c r="K25" t="n">
         <v>83</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1692</v>
+        <v>-0.3813</v>
       </c>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0211</v>
+        <v>-0.0279</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6674</v>
+        <v>-0.6635</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="N26" t="n">
         <v>51</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0406</v>
+        <v>-0.0517</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6946</v>
+        <v>-0.6969</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1254</v>
+        <v>-0.1598</v>
       </c>
       <c r="N27" t="n">
         <v>49</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0442</v>
+        <v>-0.0538</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6996</v>
+        <v>-0.7</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1365</v>
+        <v>-0.1664</v>
       </c>
       <c r="N28" t="n">
         <v>51</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2712</v>
+        <v>-0.253</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0877</v>
+        <v>-0.0818</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7604</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2712</v>
+        <v>-0.253</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8403</v>
+        <v>0.7813</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.1115</v>
+        <v>-1.0343</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8403</v>
+        <v>0.7813</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4369</v>
+        <v>0.4219</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.1115</v>
+        <v>-1.0343</v>
       </c>
       <c r="K29" t="n">
         <v>44</v>
@@ -1771,7 +1771,7 @@
         <v>122</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6745999999999999</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>166</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1017</v>
+        <v>-0.1129</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.78</v>
+        <v>-0.7831</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="N30" t="n">
         <v>51</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1112</v>
+        <v>-0.1139</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7932</v>
+        <v>-0.7844</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3437</v>
+        <v>-0.352</v>
       </c>
       <c r="N31" t="n">
         <v>49</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2084</v>
+        <v>-0.2196</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.9332</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6443</v>
+        <v>-0.6788</v>
       </c>
       <c r="N32" t="n">
         <v>49</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pancc</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2395</v>
+        <v>-0.2476</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9727</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="N33" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>pancc</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2466</v>
+        <v>-0.2484</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9822</v>
+        <v>-0.9739</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7624</v>
+        <v>-0.7681</v>
       </c>
       <c r="N34" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.768</v>
+        <v>-0.7781</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2484</v>
+        <v>-0.2517</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9847</v>
+        <v>-0.9784</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.768</v>
+        <v>-0.7781</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2329</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5351</v>
+        <v>-0.2262</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2329</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1211</v>
+        <v>-0.298</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5351</v>
+        <v>-0.2262</v>
       </c>
       <c r="K35" t="n">
         <v>83</v>
       </c>
       <c r="L35" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6562</v>
+        <v>-0.5242</v>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8138</v>
+        <v>-0.8015</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2632</v>
+        <v>-0.2592</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0054</v>
+        <v>-0.9891</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8138</v>
+        <v>-0.8015</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5668</v>
+        <v>-0.2489</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.247</v>
+        <v>-0.5526</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5668</v>
+        <v>-0.2489</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2947</v>
+        <v>-0.1344</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.247</v>
+        <v>-0.5526</v>
       </c>
       <c r="K36" t="n">
         <v>83</v>
       </c>
       <c r="L36" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5417000000000001</v>
+        <v>-0.6869999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8381</v>
+        <v>-0.8784</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2711</v>
+        <v>-0.2841</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0164</v>
+        <v>-1.0241</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8381</v>
+        <v>-0.8784</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3204</v>
+        <v>-0.323</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5177</v>
+        <v>-0.5554</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3204</v>
+        <v>-0.323</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1666</v>
+        <v>-0.1744</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5177</v>
+        <v>-0.5554</v>
       </c>
       <c r="K37" t="n">
         <v>83</v>
@@ -2139,7 +2139,7 @@
         <v>48</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6843</v>
+        <v>-0.7298</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2814</v>
+        <v>-0.2849</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0307</v>
+        <v>-1.0252</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8699</v>
+        <v>-0.8809</v>
       </c>
       <c r="N38" t="n">
         <v>49</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3175</v>
+        <v>-0.3197</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0812</v>
+        <v>-1.0741</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9816</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>78</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.9137</v>
+        <v>-2.6885</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9424</v>
+        <v>-0.8696</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.9534</v>
+        <v>-1.8481</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.9137</v>
+        <v>-2.6885</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.8864</v>
+        <v>-2.6728</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0273</v>
+        <v>-0.0157</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.8864</v>
+        <v>-2.6728</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5008</v>
+        <v>-1.4433</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0273</v>
+        <v>-0.0157</v>
       </c>
       <c r="K40" t="n">
         <v>83</v>
@@ -2277,7 +2277,7 @@
         <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5281</v>
+        <v>-1.459</v>
       </c>
       <c r="N40" t="n">
         <v>131</v>
@@ -2383,10 +2383,10 @@
         <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.215</v>
+        <v>0.206</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>0.74</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2665</v>
+        <v>-0.286</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.33</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>0.73</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2757</v>
+        <v>-0.295</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.514</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3788</v>
+        <v>-0.3945</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.576</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3975</v>
+        <v>-0.4123</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.95</v>
+        <v>-8.246</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9845</v>
+        <v>0.9732</v>
       </c>
       <c r="J7" t="n">
-        <v>19.69</v>
+        <v>19.464</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>0.768</v>
+        <v>0.7664</v>
       </c>
       <c r="J8" t="n">
-        <v>15.36</v>
+        <v>15.328</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4958</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>9.916</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2441</v>
+        <v>0.268</v>
       </c>
       <c r="J10" t="n">
-        <v>4.882</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0318</v>
+        <v>0.0541</v>
       </c>
       <c r="J11" t="n">
-        <v>0.636</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1965</v>
+        <v>1.2214</v>
       </c>
       <c r="J12" t="n">
-        <v>32.3055</v>
+        <v>32.9778</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6256</v>
+        <v>0.6052</v>
       </c>
       <c r="J13" t="n">
-        <v>16.8912</v>
+        <v>16.3404</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J14" t="n">
-        <v>16.2675</v>
+        <v>15.7815</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4809</v>
+        <v>0.4749</v>
       </c>
       <c r="J15" t="n">
-        <v>12.9843</v>
+        <v>12.8223</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0571</v>
+        <v>-0.0395</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5417</v>
+        <v>-1.0665</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.14</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3588</v>
+        <v>0.3522</v>
       </c>
       <c r="J17" t="n">
-        <v>9.6876</v>
+        <v>9.509399999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0264</v>
+        <v>-0.0354</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7128</v>
+        <v>-0.9558</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1244</v>
+        <v>-0.1394</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.3588</v>
+        <v>-3.7638</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>0.86</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1662</v>
+        <v>-0.1822</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.4874</v>
+        <v>-4.9194</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3904</v>
+        <v>-0.4019</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.5408</v>
+        <v>-10.8513</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9333</v>
+        <v>0.8757</v>
       </c>
       <c r="J22" t="n">
-        <v>25.1991</v>
+        <v>23.6439</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7043</v>
+        <v>0.6735</v>
       </c>
       <c r="J23" t="n">
-        <v>19.0161</v>
+        <v>18.1845</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5859</v>
+        <v>0.5679</v>
       </c>
       <c r="J24" t="n">
-        <v>15.8193</v>
+        <v>15.3333</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5382</v>
+        <v>0.5249</v>
       </c>
       <c r="J25" t="n">
-        <v>14.5314</v>
+        <v>14.1723</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3707</v>
+        <v>-0.3507</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.0089</v>
+        <v>-9.4689</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2312</v>
+        <v>0.2263</v>
       </c>
       <c r="J27" t="n">
-        <v>6.2424</v>
+        <v>6.1101</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1302</v>
+        <v>-0.1467</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.5154</v>
+        <v>-3.9609</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.141</v>
+        <v>-0.1577</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.807</v>
+        <v>-4.2579</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.308</v>
+        <v>-0.3238</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.742599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3175</v>
+        <v>-0.333</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.5725</v>
+        <v>-8.991</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>2.01</v>
       </c>
       <c r="I32" t="n">
-        <v>1.388</v>
+        <v>1.5216</v>
       </c>
       <c r="J32" t="n">
-        <v>24.984</v>
+        <v>27.3888</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0769</v>
+        <v>1.1933</v>
       </c>
       <c r="J33" t="n">
-        <v>19.3842</v>
+        <v>21.4794</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>1.56</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8847</v>
+        <v>0.9868</v>
       </c>
       <c r="J34" t="n">
-        <v>15.9246</v>
+        <v>17.7624</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6301</v>
+        <v>0.7088</v>
       </c>
       <c r="J35" t="n">
-        <v>11.3418</v>
+        <v>12.7584</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>1.14</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3308</v>
+        <v>0.3563</v>
       </c>
       <c r="J36" t="n">
-        <v>5.9544</v>
+        <v>6.4134</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1214</v>
+        <v>-0.1542</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.1852</v>
+        <v>-2.7756</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3194</v>
+        <v>-0.3435</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.7492</v>
+        <v>-6.183</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>0.55</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4122</v>
+        <v>-0.4316</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.4196</v>
+        <v>-7.7688</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5274</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.2628</v>
+        <v>-9.4932</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.35</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6015</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.827</v>
+        <v>-10.9332</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6259</v>
+        <v>0.6896</v>
       </c>
       <c r="J42" t="n">
-        <v>18.777</v>
+        <v>20.688</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5692</v>
+        <v>0.6271</v>
       </c>
       <c r="J43" t="n">
-        <v>17.076</v>
+        <v>18.813</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.467</v>
+        <v>0.5133</v>
       </c>
       <c r="J44" t="n">
-        <v>14.01</v>
+        <v>15.399</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1543</v>
+        <v>-0.1522</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.629</v>
+        <v>-4.566</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.719</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.271</v>
+        <v>-21.57</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3849</v>
+        <v>0.4159</v>
       </c>
       <c r="J47" t="n">
-        <v>11.547</v>
+        <v>12.477</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.03</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
-        <v>2.754</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0205</v>
+        <v>-0.0252</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.615</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0759</v>
+        <v>-0.0861</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.277</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1983</v>
+        <v>-0.2119</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.949</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>2.07</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4868</v>
+        <v>1.6196</v>
       </c>
       <c r="J52" t="n">
-        <v>32.7096</v>
+        <v>35.6312</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.57</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9112</v>
+        <v>1.0121</v>
       </c>
       <c r="J53" t="n">
-        <v>20.0464</v>
+        <v>22.2662</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>1.36</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6581</v>
+        <v>0.7361</v>
       </c>
       <c r="J54" t="n">
-        <v>14.4782</v>
+        <v>16.1942</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>1.25</v>
       </c>
       <c r="I55" t="n">
-        <v>0.512</v>
+        <v>0.5742</v>
       </c>
       <c r="J55" t="n">
-        <v>11.264</v>
+        <v>12.6324</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.86</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5165</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.408</v>
+        <v>-11.363</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>0.85</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1485</v>
+        <v>-0.171</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.267</v>
+        <v>-3.762</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2228</v>
+        <v>-0.2442</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.9016</v>
+        <v>-5.3724</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2328</v>
+        <v>-0.254</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.1216</v>
+        <v>-5.588</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4096</v>
+        <v>-0.4248</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.011200000000001</v>
+        <v>-9.345599999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4189</v>
+        <v>-0.4337</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.2158</v>
+        <v>-9.541399999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3684</v>
+        <v>0.3929</v>
       </c>
       <c r="J62" t="n">
-        <v>13.2624</v>
+        <v>14.1444</v>
       </c>
     </row>
     <row r="63">
@@ -4823,10 +4823,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2795</v>
+        <v>0.2859</v>
       </c>
       <c r="J63" t="n">
-        <v>10.062</v>
+        <v>10.2924</v>
       </c>
     </row>
     <row r="64">
@@ -4863,10 +4863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0877</v>
+        <v>-0.0987</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.1572</v>
+        <v>-3.5532</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>0.93</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1112</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.5856</v>
+        <v>-4.0032</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.71</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3263</v>
+        <v>-0.3381</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.7468</v>
+        <v>-12.1716</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4107</v>
+        <v>0.461</v>
       </c>
       <c r="J67" t="n">
-        <v>14.7852</v>
+        <v>16.596</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2504</v>
+        <v>0.2639</v>
       </c>
       <c r="J68" t="n">
-        <v>9.0144</v>
+        <v>9.500400000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.043</v>
+        <v>0.0516</v>
       </c>
       <c r="J69" t="n">
-        <v>1.548</v>
+        <v>1.8576</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1049</v>
+        <v>-0.1153</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.7764</v>
+        <v>-4.1508</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2542</v>
+        <v>-0.2664</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.151199999999999</v>
+        <v>-9.590400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1908</v>
+        <v>1.306</v>
       </c>
       <c r="J72" t="n">
-        <v>29.77</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.66</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0362</v>
+        <v>1.1424</v>
       </c>
       <c r="J73" t="n">
-        <v>25.905</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6661</v>
+        <v>0.7429</v>
       </c>
       <c r="J74" t="n">
-        <v>16.6525</v>
+        <v>18.5725</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2125</v>
+        <v>-0.1929</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.3125</v>
+        <v>-4.8225</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5452</v>
+        <v>-0.5032</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.63</v>
+        <v>-12.58</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.577</v>
+        <v>0.6311</v>
       </c>
       <c r="J77" t="n">
-        <v>14.425</v>
+        <v>15.7775</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1887</v>
+        <v>-0.2069</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.7175</v>
+        <v>-5.1725</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2173</v>
+        <v>-0.2356</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.4325</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3513</v>
+        <v>-0.3663</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.782500000000001</v>
+        <v>-9.157500000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.49</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5092</v>
+        <v>-0.5162</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.73</v>
+        <v>-12.905</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9646</v>
+        <v>0.8961</v>
       </c>
       <c r="J82" t="n">
-        <v>27.9734</v>
+        <v>25.9869</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3054</v>
+        <v>0.3053</v>
       </c>
       <c r="J83" t="n">
-        <v>8.8566</v>
+        <v>8.8537</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1865</v>
+        <v>0.193</v>
       </c>
       <c r="J84" t="n">
-        <v>5.4085</v>
+        <v>5.597</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.99</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0643</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.8647</v>
+        <v>-1.9169</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.76</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7379</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-21.3991</v>
+        <v>-19.952</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4453</v>
+        <v>0.4386</v>
       </c>
       <c r="J87" t="n">
-        <v>12.9137</v>
+        <v>12.7194</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3315</v>
+        <v>0.3323</v>
       </c>
       <c r="J88" t="n">
-        <v>9.6135</v>
+        <v>9.636699999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0861</v>
+        <v>-0.0975</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.4969</v>
+        <v>-2.8275</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.196</v>
+        <v>-0.2101</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.684</v>
+        <v>-6.0929</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2566</v>
+        <v>-0.2702</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.4414</v>
+        <v>-7.8358</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>0.98</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0051</v>
+        <v>-0.0188</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.1224</v>
+        <v>-0.4512</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>0.82</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1953</v>
+        <v>-0.2142</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.6872</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2052</v>
+        <v>-0.2241</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.9248</v>
+        <v>-5.3784</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2427</v>
+        <v>-0.2615</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.8248</v>
+        <v>-6.276</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4312</v>
+        <v>-0.4433</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.3488</v>
+        <v>-10.6392</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3146</v>
+        <v>1.2916</v>
       </c>
       <c r="J97" t="n">
-        <v>31.5504</v>
+        <v>30.9984</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7347</v>
+        <v>0.7036</v>
       </c>
       <c r="J98" t="n">
-        <v>17.6328</v>
+        <v>16.8864</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6219</v>
+        <v>0.6028</v>
       </c>
       <c r="J99" t="n">
-        <v>14.9256</v>
+        <v>14.4672</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.21</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5745</v>
+        <v>0.5603</v>
       </c>
       <c r="J100" t="n">
-        <v>13.788</v>
+        <v>13.4472</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3585</v>
+        <v>-0.3355</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3162</v>
+        <v>0.3168</v>
       </c>
       <c r="J102" t="n">
-        <v>9.486000000000001</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1697</v>
+        <v>0.1759</v>
       </c>
       <c r="J103" t="n">
-        <v>5.091</v>
+        <v>5.277</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.546</v>
+        <v>-0.705</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.546</v>
+        <v>-0.705</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.37</v>
+        <v>-0.381</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.1</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8838</v>
+        <v>0.8282</v>
       </c>
       <c r="J107" t="n">
-        <v>26.514</v>
+        <v>24.846</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8371</v>
+        <v>0.7875</v>
       </c>
       <c r="J108" t="n">
-        <v>25.113</v>
+        <v>23.625</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4224</v>
+        <v>0.4176</v>
       </c>
       <c r="J109" t="n">
-        <v>12.672</v>
+        <v>12.528</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3169</v>
+        <v>0.3201</v>
       </c>
       <c r="J110" t="n">
-        <v>9.507</v>
+        <v>9.603</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6593</v>
+        <v>-0.6142</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.779</v>
+        <v>-18.426</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4115</v>
+        <v>1.3983</v>
       </c>
       <c r="J112" t="n">
-        <v>33.876</v>
+        <v>33.5592</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>1.72</v>
       </c>
       <c r="I113" t="n">
-        <v>1.3761</v>
+        <v>1.3608</v>
       </c>
       <c r="J113" t="n">
-        <v>33.0264</v>
+        <v>32.6592</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6032</v>
+        <v>0.5899</v>
       </c>
       <c r="J114" t="n">
-        <v>14.4768</v>
+        <v>14.1576</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3502</v>
+        <v>0.3618</v>
       </c>
       <c r="J115" t="n">
-        <v>8.4048</v>
+        <v>8.683199999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3493</v>
+        <v>-0.322</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.3832</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4516</v>
+        <v>0.4285</v>
       </c>
       <c r="J117" t="n">
-        <v>10.8384</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1331</v>
+        <v>-0.1516</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.1944</v>
+        <v>-3.6384</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2719</v>
+        <v>-0.2901</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.5256</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>0.66</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3478</v>
+        <v>-0.3636</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.347200000000001</v>
+        <v>-8.7264</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.54</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4599</v>
+        <v>-0.4704</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.0376</v>
+        <v>-11.2896</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4887</v>
+        <v>0.4774</v>
       </c>
       <c r="J122" t="n">
-        <v>14.661</v>
+        <v>14.322</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1243</v>
+        <v>0.1305</v>
       </c>
       <c r="J123" t="n">
-        <v>3.729</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0178</v>
+        <v>-0.0232</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.534</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1731</v>
+        <v>-0.1875</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.193</v>
+        <v>-5.625</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3319</v>
+        <v>-0.3442</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.957000000000001</v>
+        <v>-10.326</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6662</v>
+        <v>0.6332</v>
       </c>
       <c r="J127" t="n">
-        <v>19.986</v>
+        <v>18.996</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.12</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3819</v>
+        <v>0.3775</v>
       </c>
       <c r="J128" t="n">
-        <v>11.457</v>
+        <v>11.325</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2427</v>
+        <v>0.2477</v>
       </c>
       <c r="J129" t="n">
-        <v>7.281</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1819</v>
+        <v>0.1899</v>
       </c>
       <c r="J130" t="n">
-        <v>5.457</v>
+        <v>5.697</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3413</v>
+        <v>-0.3301</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.239</v>
+        <v>-9.903</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.79</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2374</v>
+        <v>1.2181</v>
       </c>
       <c r="J132" t="n">
-        <v>37.122</v>
+        <v>36.543</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>0.89</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1473</v>
+        <v>-0.1598</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.419</v>
+        <v>-4.794</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1689</v>
+        <v>-0.1818</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.067</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2209</v>
+        <v>-0.234</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.627</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3192</v>
+        <v>-0.3308</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.576000000000001</v>
+        <v>-9.923999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1153</v>
+        <v>1.071</v>
       </c>
       <c r="J137" t="n">
-        <v>33.459</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5819</v>
+        <v>0.5601</v>
       </c>
       <c r="J138" t="n">
-        <v>17.457</v>
+        <v>16.803</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0308</v>
+        <v>0.0433</v>
       </c>
       <c r="J139" t="n">
-        <v>0.924</v>
+        <v>1.299</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.361</v>
+        <v>-2.283</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.491</v>
+        <v>-0.4652</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.73</v>
+        <v>-13.956</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2267</v>
+        <v>1.1961</v>
       </c>
       <c r="J142" t="n">
-        <v>30.6675</v>
+        <v>29.9025</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9655</v>
+        <v>0.9082</v>
       </c>
       <c r="J143" t="n">
-        <v>24.1375</v>
+        <v>22.705</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.485</v>
+        <v>0.4778</v>
       </c>
       <c r="J144" t="n">
-        <v>12.125</v>
+        <v>11.945</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2115</v>
+        <v>0.2263</v>
       </c>
       <c r="J145" t="n">
-        <v>5.2875</v>
+        <v>5.6575</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.464</v>
+        <v>-0.4347</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6</v>
+        <v>-10.8675</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5535</v>
+        <v>0.5285</v>
       </c>
       <c r="J147" t="n">
-        <v>13.8375</v>
+        <v>13.2125</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1093</v>
+        <v>-0.1249</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.7325</v>
+        <v>-3.1225</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1822</v>
+        <v>-0.1994</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.555</v>
+        <v>-4.985</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3379</v>
+        <v>-0.3524</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.4475</v>
+        <v>-8.81</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3756</v>
+        <v>-0.3887</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.717499999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.489</v>
+        <v>0.4707</v>
       </c>
       <c r="J152" t="n">
-        <v>11.247</v>
+        <v>10.8261</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3295</v>
+        <v>0.3223</v>
       </c>
       <c r="J153" t="n">
-        <v>7.5785</v>
+        <v>7.4129</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2727</v>
+        <v>-0.2887</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.2721</v>
+        <v>-6.6401</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3016</v>
+        <v>-0.317</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.9368</v>
+        <v>-7.291</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4333</v>
+        <v>-0.4434</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.9659</v>
+        <v>-10.1982</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0192</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>23.4416</v>
+        <v>22.2686</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="J158" t="n">
-        <v>21.8293</v>
+        <v>20.5942</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>1.35</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8862</v>
+        <v>0.838</v>
       </c>
       <c r="J159" t="n">
-        <v>20.3826</v>
+        <v>19.274</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>1.28</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7319</v>
+        <v>0.7018</v>
       </c>
       <c r="J160" t="n">
-        <v>16.8337</v>
+        <v>16.1414</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.236</v>
+        <v>-0.2187</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.428</v>
+        <v>-5.0301</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.84</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5518</v>
+        <v>1.5403</v>
       </c>
       <c r="J162" t="n">
-        <v>41.8986</v>
+        <v>41.5881</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8526</v>
+        <v>0.8065</v>
       </c>
       <c r="J163" t="n">
-        <v>23.0202</v>
+        <v>21.7755</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5789</v>
+        <v>0.5633</v>
       </c>
       <c r="J164" t="n">
-        <v>15.6303</v>
+        <v>15.2091</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.98</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1532</v>
+        <v>-0.1408</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.1364</v>
+        <v>-3.8016</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6572</v>
+        <v>-0.6079</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.7444</v>
+        <v>-16.4133</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1302</v>
+        <v>0.1278</v>
       </c>
       <c r="J167" t="n">
-        <v>3.5154</v>
+        <v>3.4506</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>0.91</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1093</v>
+        <v>-0.1249</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.9511</v>
+        <v>-3.3723</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1314</v>
+        <v>-0.1476</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.5478</v>
+        <v>-3.9852</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2611</v>
+        <v>-0.2778</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.0497</v>
+        <v>-7.5006</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.71</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3093</v>
+        <v>-0.3248</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.351100000000001</v>
+        <v>-8.769600000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4717</v>
+        <v>1.4655</v>
       </c>
       <c r="J172" t="n">
-        <v>27.9623</v>
+        <v>27.8445</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1339</v>
+        <v>1.1051</v>
       </c>
       <c r="J173" t="n">
-        <v>21.5441</v>
+        <v>20.9969</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.47</v>
       </c>
       <c r="I174" t="n">
-        <v>1.0627</v>
+        <v>1.0249</v>
       </c>
       <c r="J174" t="n">
-        <v>20.1913</v>
+        <v>19.4731</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9009</v>
+        <v>0.8566</v>
       </c>
       <c r="J175" t="n">
-        <v>17.1171</v>
+        <v>16.2754</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0959</v>
+        <v>0.13</v>
       </c>
       <c r="J176" t="n">
-        <v>1.8221</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>0.86</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1076</v>
+        <v>-0.1366</v>
       </c>
       <c r="J177" t="n">
-        <v>-2.0444</v>
+        <v>-2.5954</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>0.79</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1881</v>
+        <v>-0.2151</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.5739</v>
+        <v>-4.0869</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3124</v>
+        <v>-0.3346</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.9356</v>
+        <v>-6.3574</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.468</v>
+        <v>-0.4825</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.891999999999999</v>
+        <v>-9.1675</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.26</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6968</v>
+        <v>-0.6934</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.2392</v>
+        <v>-13.1746</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4290/event_4290_evp_summary.xlsx
+++ b/database/event/4290/event_4290_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9952</v>
+        <v>6.0117</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9391</v>
+        <v>1.9445</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1049</v>
+        <v>2.1328</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9952</v>
+        <v>6.0117</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1681</v>
+        <v>2.2609</v>
       </c>
       <c r="G2" t="n">
-        <v>3.827</v>
+        <v>3.7509</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2593</v>
+        <v>2.2609</v>
       </c>
       <c r="I2" t="n">
-        <v>1.22</v>
+        <v>1.2694</v>
       </c>
       <c r="J2" t="n">
-        <v>3.827</v>
+        <v>3.7509</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>5.047</v>
+        <v>5.020300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>208</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.396</v>
+        <v>5.3257</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7453</v>
+        <v>1.7226</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8322</v>
+        <v>1.8203</v>
       </c>
       <c r="E3" t="n">
-        <v>5.396</v>
+        <v>5.3257</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2307</v>
+        <v>2.3412</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1653</v>
+        <v>2.9845</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4656</v>
+        <v>2.3472</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3314</v>
+        <v>1.3179</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1653</v>
+        <v>2.9845</v>
       </c>
       <c r="K3" t="n">
         <v>44</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4967</v>
+        <v>4.3024</v>
       </c>
       <c r="N3" t="n">
         <v>166</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5343</v>
+        <v>4.7159</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4666</v>
+        <v>1.5253</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4399</v>
+        <v>1.5425</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5343</v>
+        <v>4.7159</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1672</v>
+        <v>2.302</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3671</v>
+        <v>2.4139</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2561</v>
+        <v>2.302</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2183</v>
+        <v>1.2925</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3671</v>
+        <v>2.4139</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5854</v>
+        <v>3.7064</v>
       </c>
       <c r="N4" t="n">
         <v>208</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5279</v>
+        <v>4.5399</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4645</v>
+        <v>1.4684</v>
       </c>
       <c r="D5" t="n">
-        <v>1.437</v>
+        <v>1.4624</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5279</v>
+        <v>4.5399</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9773</v>
+        <v>2.417</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5506</v>
+        <v>2.1229</v>
       </c>
       <c r="H5" t="n">
-        <v>4.929</v>
+        <v>2.632</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6616</v>
+        <v>1.4778</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5506</v>
+        <v>2.1229</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2122</v>
+        <v>3.6007</v>
       </c>
       <c r="N5" t="n">
         <v>166</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.504</v>
+        <v>4.4914</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4568</v>
+        <v>1.4527</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4261</v>
+        <v>1.4403</v>
       </c>
       <c r="E6" t="n">
-        <v>4.504</v>
+        <v>4.4914</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3268</v>
+        <v>2.9994</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1772</v>
+        <v>1.492</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7828</v>
+        <v>4.8186</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5027</v>
+        <v>2.7055</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1772</v>
+        <v>1.492</v>
       </c>
       <c r="K6" t="n">
         <v>44</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6799</v>
+        <v>4.1975</v>
       </c>
       <c r="N6" t="n">
         <v>166</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8185</v>
+        <v>3.8171</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2351</v>
+        <v>1.2346</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1141</v>
+        <v>1.1331</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8185</v>
+        <v>3.8171</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4637</v>
+        <v>1.5123</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3548</v>
+        <v>2.3048</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4637</v>
+        <v>1.5123</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7904</v>
+        <v>0.8491</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3548</v>
+        <v>2.3048</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1452</v>
+        <v>3.1539</v>
       </c>
       <c r="N7" t="n">
         <v>208</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2201</v>
+        <v>3.1075</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0415</v>
+        <v>1.0051</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8417</v>
+        <v>0.8098</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2201</v>
+        <v>3.1075</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9226</v>
+        <v>1.7698</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2975</v>
+        <v>1.3377</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9226</v>
+        <v>1.7698</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0382</v>
+        <v>0.9937</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2975</v>
+        <v>1.3377</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3357</v>
+        <v>2.3314</v>
       </c>
       <c r="N8" t="n">
         <v>166</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0487</v>
+        <v>2.8937</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9861</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7124</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0487</v>
+        <v>2.8937</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1391</v>
+        <v>1.9837</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9096</v>
+        <v>0.91</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1636</v>
+        <v>1.9837</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1683</v>
+        <v>1.1138</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9096</v>
+        <v>0.91</v>
       </c>
       <c r="K9" t="n">
         <v>51</v>
@@ -851,7 +851,7 @@
         <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0779</v>
+        <v>2.0238</v>
       </c>
       <c r="N9" t="n">
         <v>208</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.631</v>
+        <v>2.4475</v>
       </c>
       <c r="C10" t="n">
-        <v>0.851</v>
+        <v>0.7916</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5735</v>
+        <v>0.5092</v>
       </c>
       <c r="E10" t="n">
-        <v>2.631</v>
+        <v>2.4475</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1306</v>
+        <v>1.949</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5004</v>
+        <v>0.4985</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1356</v>
+        <v>1.949</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1532</v>
+        <v>1.0943</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5004</v>
+        <v>0.4985</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6536</v>
+        <v>1.5928</v>
       </c>
       <c r="N10" t="n">
         <v>208</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2643</v>
+        <v>2.1572</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.6977</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4066</v>
+        <v>0.3769</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2643</v>
+        <v>2.1572</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7941</v>
+        <v>2.1572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4702</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7941</v>
+        <v>2.1572</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9688</v>
+        <v>2.1572</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4702</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>83</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.1572</v>
+      </c>
+      <c r="N11" t="n">
         <v>83</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="N11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2595</v>
+        <v>2.0687</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7308</v>
+        <v>0.6691</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4044</v>
+        <v>0.3366</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2595</v>
+        <v>2.0687</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2595</v>
+        <v>1.6608</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.4079</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2595</v>
+        <v>1.6608</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2595</v>
+        <v>0.9325</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.4079</v>
       </c>
       <c r="K12" t="n">
         <v>83</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2595</v>
+        <v>1.3404</v>
       </c>
       <c r="N12" t="n">
-        <v>83</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.545</v>
+        <v>1.5848</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4997</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0791</v>
+        <v>0.1162</v>
       </c>
       <c r="E13" t="n">
-        <v>1.545</v>
+        <v>1.5848</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2385</v>
+        <v>2.2746</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6935</v>
+        <v>-0.6898</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4915</v>
+        <v>2.2746</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3454</v>
+        <v>1.2771</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6935</v>
+        <v>-0.6898</v>
       </c>
       <c r="K13" t="n">
         <v>134</v>
@@ -1035,7 +1035,7 @@
         <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6518999999999999</v>
+        <v>0.5872999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>182</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4664</v>
+        <v>0.4615</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0323</v>
+        <v>0.0442</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4421</v>
+        <v>1.4269</v>
       </c>
       <c r="N14" t="n">
         <v>83</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4155</v>
+        <v>1.3356</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4578</v>
+        <v>0.432</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0202</v>
+        <v>0.0026</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4155</v>
+        <v>1.3356</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4697</v>
+        <v>1.3356</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0542</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4697</v>
+        <v>1.3356</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7936</v>
+        <v>1.3356</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0542</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7393999999999999</v>
+        <v>1.3356</v>
       </c>
       <c r="N15" t="n">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4004</v>
+        <v>1.3239</v>
       </c>
       <c r="C16" t="n">
-        <v>0.453</v>
+        <v>0.4282</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0133</v>
+        <v>-0.0027</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4004</v>
+        <v>1.3239</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4004</v>
+        <v>1.3817</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.0578</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4004</v>
+        <v>1.3817</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4004</v>
+        <v>0.7758</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.0578</v>
       </c>
       <c r="K16" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4004</v>
+        <v>0.7180000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1016</v>
+        <v>0.9176</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3563</v>
+        <v>0.2968</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1227</v>
+        <v>-0.1878</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1016</v>
+        <v>0.9176</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8289</v>
+        <v>0.9176</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7272999999999999</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8289</v>
+        <v>0.9176</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9876</v>
+        <v>0.9176</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7272999999999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L17" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2603000000000001</v>
+        <v>0.9176</v>
       </c>
       <c r="N17" t="n">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9447</v>
+        <v>0.8655</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3056</v>
+        <v>0.2799</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1942</v>
+        <v>-0.2115</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9447</v>
+        <v>0.8655</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9447</v>
+        <v>1.5413</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.6758</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9447</v>
+        <v>1.5413</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9447</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.6758</v>
       </c>
       <c r="K18" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9447</v>
+        <v>0.1896</v>
       </c>
       <c r="N18" t="n">
-        <v>78</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2891</v>
+        <v>0.2685</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2174</v>
+        <v>-0.2276</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8937</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>78</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1495</v>
+        <v>0.1503</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4138</v>
+        <v>-0.3941</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4621</v>
+        <v>0.4646</v>
       </c>
       <c r="N20" t="n">
         <v>78</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.329</v>
+        <v>0.2738</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1064</v>
+        <v>0.0886</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4744</v>
+        <v>-0.4811</v>
       </c>
       <c r="E21" t="n">
-        <v>0.329</v>
+        <v>0.2738</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7572</v>
+        <v>0.2738</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4282</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7572</v>
+        <v>0.2738</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4089</v>
+        <v>0.2738</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4282</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>83</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="N21" t="n">
         <v>83</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-0.01930000000000004</v>
-      </c>
-      <c r="N21" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0848</v>
+        <v>0.0703</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5048</v>
+        <v>-0.5068</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2623</v>
+        <v>0.2172</v>
       </c>
       <c r="N22" t="n">
         <v>49</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2595</v>
+        <v>0.2158</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0839</v>
+        <v>0.0698</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5061</v>
+        <v>-0.5075</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2595</v>
+        <v>0.2158</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2595</v>
+        <v>0.6271</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2595</v>
+        <v>0.6271</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2595</v>
+        <v>0.3521</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="K23" t="n">
         <v>83</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2595</v>
+        <v>-0.05919999999999997</v>
       </c>
       <c r="N23" t="n">
-        <v>83</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0427</v>
+        <v>0.0431</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5641</v>
+        <v>-0.5451</v>
       </c>
       <c r="E24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="I24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.132</v>
+        <v>0.1333</v>
       </c>
       <c r="N24" t="n">
         <v>83</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0736</v>
+        <v>-0.0126</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0238</v>
+        <v>-0.0041</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5907</v>
+        <v>-0.6115</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0736</v>
+        <v>-0.0126</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9889</v>
+        <v>0.8618</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9153</v>
+        <v>-0.8744</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9889</v>
+        <v>0.8618</v>
       </c>
       <c r="I25" t="n">
-        <v>0.534</v>
+        <v>0.4839</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9153</v>
+        <v>-0.8744</v>
       </c>
       <c r="K25" t="n">
         <v>83</v>
@@ -1587,7 +1587,7 @@
         <v>83</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3813</v>
+        <v>-0.3905</v>
       </c>
       <c r="N25" t="n">
         <v>166</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0279</v>
+        <v>-0.0326</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6635</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0864</v>
+        <v>-0.1008</v>
       </c>
       <c r="N26" t="n">
         <v>51</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0517</v>
+        <v>-0.0433</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6969</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1598</v>
+        <v>-0.1339</v>
       </c>
       <c r="N27" t="n">
         <v>49</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0538</v>
+        <v>-0.0459</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7</v>
+        <v>-0.6705</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1664</v>
+        <v>-0.142</v>
       </c>
       <c r="N28" t="n">
         <v>51</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.253</v>
+        <v>-0.2228</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0818</v>
+        <v>-0.0721</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7073</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.253</v>
+        <v>-0.2228</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7813</v>
+        <v>0.8072</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.0343</v>
+        <v>-1.03</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7813</v>
+        <v>0.8072</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4219</v>
+        <v>0.4532</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.0343</v>
+        <v>-1.03</v>
       </c>
       <c r="K29" t="n">
         <v>44</v>
@@ -1771,7 +1771,7 @@
         <v>122</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.5768</v>
       </c>
       <c r="N29" t="n">
         <v>166</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1129</v>
+        <v>-0.1023</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7831</v>
+        <v>-0.7499</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.349</v>
+        <v>-0.3163</v>
       </c>
       <c r="N30" t="n">
         <v>51</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1139</v>
+        <v>-0.1233</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7844</v>
+        <v>-0.7794</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.352</v>
+        <v>-0.3812</v>
       </c>
       <c r="N31" t="n">
         <v>49</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2196</v>
+        <v>-0.2113</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9332</v>
+        <v>-0.9034</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6788</v>
+        <v>-0.6533</v>
       </c>
       <c r="N32" t="n">
         <v>49</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2476</v>
+        <v>-0.2222</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9727</v>
+        <v>-0.9187</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7655</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>83</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2484</v>
+        <v>-0.2406</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9739</v>
+        <v>-0.9447</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7681</v>
+        <v>-0.7439</v>
       </c>
       <c r="N34" t="n">
         <v>51</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7781</v>
+        <v>-0.7724</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2517</v>
+        <v>-0.2498</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9784</v>
+        <v>-0.9577</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7781</v>
+        <v>-0.7724</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5017</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2262</v>
+        <v>-0.2707</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5017</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.298</v>
+        <v>-0.2817</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2262</v>
+        <v>-0.2707</v>
       </c>
       <c r="K35" t="n">
         <v>83</v>
@@ -2047,7 +2047,7 @@
         <v>83</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5242</v>
+        <v>-0.5524</v>
       </c>
       <c r="N35" t="n">
         <v>166</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8015</v>
+        <v>-0.7943</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2592</v>
+        <v>-0.2569</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9891</v>
+        <v>-0.9676</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8015</v>
+        <v>-0.7943</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2489</v>
+        <v>-0.2476</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5526</v>
+        <v>-0.5467</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2489</v>
+        <v>-0.2476</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1344</v>
+        <v>-0.139</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5526</v>
+        <v>-0.5467</v>
       </c>
       <c r="K36" t="n">
         <v>83</v>
@@ -2093,7 +2093,7 @@
         <v>48</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6869999999999999</v>
+        <v>-0.6857</v>
       </c>
       <c r="N36" t="n">
         <v>131</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8784</v>
+        <v>-0.7956</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2841</v>
+        <v>-0.2573</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0241</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8784</v>
+        <v>-0.7956</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.323</v>
+        <v>-0.2693</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5554</v>
+        <v>-0.5263</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.323</v>
+        <v>-0.2693</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1744</v>
+        <v>-0.1512</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5554</v>
+        <v>-0.5263</v>
       </c>
       <c r="K37" t="n">
         <v>83</v>
@@ -2139,7 +2139,7 @@
         <v>48</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7298</v>
+        <v>-0.6775</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2849</v>
+        <v>-0.2878</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0252</v>
+        <v>-1.0111</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8809</v>
+        <v>-0.8897</v>
       </c>
       <c r="N38" t="n">
         <v>49</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3197</v>
+        <v>-0.301</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0741</v>
+        <v>-1.0298</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="N39" t="n">
         <v>78</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6885</v>
+        <v>-2.4722</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8696</v>
+        <v>-0.7996</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.8481</v>
+        <v>-1.732</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6885</v>
+        <v>-2.4722</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.6728</v>
+        <v>-2.4055</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0157</v>
+        <v>-0.0667</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.6728</v>
+        <v>-2.4055</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4433</v>
+        <v>-1.3506</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0157</v>
+        <v>-0.0667</v>
       </c>
       <c r="K40" t="n">
         <v>83</v>
@@ -2277,7 +2277,7 @@
         <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.459</v>
+        <v>-1.4173</v>
       </c>
       <c r="N40" t="n">
         <v>131</v>
@@ -2383,10 +2383,10 @@
         <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.206</v>
+        <v>0.1985</v>
       </c>
       <c r="J2" t="n">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>0.74</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.286</v>
+        <v>-0.2701</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.72</v>
+        <v>-5.402</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>0.73</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.295</v>
+        <v>-0.2792</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.9</v>
+        <v>-5.584</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3945</v>
+        <v>-0.3827</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.89</v>
+        <v>-7.654</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4123</v>
+        <v>-0.4019</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.246</v>
+        <v>-8.038</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9732</v>
+        <v>0.9061</v>
       </c>
       <c r="J7" t="n">
-        <v>19.464</v>
+        <v>18.122</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7664</v>
+        <v>0.6953</v>
       </c>
       <c r="J8" t="n">
-        <v>15.328</v>
+        <v>13.906</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4473</v>
       </c>
       <c r="J9" t="n">
-        <v>10.212</v>
+        <v>8.946</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.268</v>
+        <v>0.2216</v>
       </c>
       <c r="J10" t="n">
-        <v>5.36</v>
+        <v>4.432</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0541</v>
+        <v>0.0348</v>
       </c>
       <c r="J11" t="n">
-        <v>1.082</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2214</v>
+        <v>1.2392</v>
       </c>
       <c r="J12" t="n">
-        <v>32.9778</v>
+        <v>33.4584</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6052</v>
+        <v>0.574</v>
       </c>
       <c r="J13" t="n">
-        <v>16.3404</v>
+        <v>15.498</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J14" t="n">
-        <v>15.7815</v>
+        <v>14.9256</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4749</v>
+        <v>0.4418</v>
       </c>
       <c r="J15" t="n">
-        <v>12.8223</v>
+        <v>11.9286</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0395</v>
+        <v>-0.0341</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0665</v>
+        <v>-0.9207</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.14</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3522</v>
+        <v>0.2994</v>
       </c>
       <c r="J17" t="n">
-        <v>9.509399999999999</v>
+        <v>8.0838</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0354</v>
+        <v>-0.0276</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9558</v>
+        <v>-0.7452</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1394</v>
+        <v>-0.1219</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7638</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>0.86</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1822</v>
+        <v>-0.1629</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.9194</v>
+        <v>-4.3983</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4019</v>
+        <v>-0.391</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.8513</v>
+        <v>-10.557</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8757</v>
+        <v>0.8563</v>
       </c>
       <c r="J22" t="n">
-        <v>23.6439</v>
+        <v>23.1201</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6735</v>
+        <v>0.642</v>
       </c>
       <c r="J23" t="n">
-        <v>18.1845</v>
+        <v>17.334</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5679</v>
+        <v>0.5334</v>
       </c>
       <c r="J24" t="n">
-        <v>15.3333</v>
+        <v>14.4018</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5249</v>
+        <v>0.4898</v>
       </c>
       <c r="J25" t="n">
-        <v>14.1723</v>
+        <v>13.2246</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3507</v>
+        <v>-0.3096</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.4689</v>
+        <v>-8.3592</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2263</v>
+        <v>0.1841</v>
       </c>
       <c r="J27" t="n">
-        <v>6.1101</v>
+        <v>4.9707</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.9609</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1577</v>
+        <v>-0.1407</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.2579</v>
+        <v>-3.7989</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3238</v>
+        <v>-0.307</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.742599999999999</v>
+        <v>-8.289</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.333</v>
+        <v>-0.3168</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.991</v>
+        <v>-8.553599999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>2.01</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5216</v>
+        <v>1.5408</v>
       </c>
       <c r="J32" t="n">
-        <v>27.3888</v>
+        <v>27.7344</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.73</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1933</v>
+        <v>1.1922</v>
       </c>
       <c r="J33" t="n">
-        <v>21.4794</v>
+        <v>21.4596</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>1.56</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9868</v>
+        <v>0.9812</v>
       </c>
       <c r="J34" t="n">
-        <v>17.7624</v>
+        <v>17.6616</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7088</v>
+        <v>0.7042</v>
       </c>
       <c r="J35" t="n">
-        <v>12.7584</v>
+        <v>12.6756</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>1.14</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3563</v>
+        <v>0.3221</v>
       </c>
       <c r="J36" t="n">
-        <v>6.4134</v>
+        <v>5.7978</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1542</v>
+        <v>-0.1316</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.7756</v>
+        <v>-2.3688</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3435</v>
+        <v>-0.335</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.183</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>0.55</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4316</v>
+        <v>-0.4263</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.7688</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.44</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5274</v>
+        <v>-0.5286</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.4932</v>
+        <v>-9.514799999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.35</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.6194</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.9332</v>
+        <v>-11.1492</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6896</v>
+        <v>0.6743</v>
       </c>
       <c r="J42" t="n">
-        <v>20.688</v>
+        <v>20.229</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6271</v>
+        <v>0.6135</v>
       </c>
       <c r="J43" t="n">
-        <v>18.813</v>
+        <v>18.405</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5133</v>
+        <v>0.4983</v>
       </c>
       <c r="J44" t="n">
-        <v>15.399</v>
+        <v>14.949</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1522</v>
+        <v>-0.1211</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.566</v>
+        <v>-3.633</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.719</v>
+        <v>-0.6889</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.57</v>
+        <v>-20.667</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4159</v>
+        <v>0.3596</v>
       </c>
       <c r="J47" t="n">
-        <v>12.477</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.03</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0.0738</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0252</v>
+        <v>-0.0181</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.756</v>
+        <v>-0.543</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0861</v>
+        <v>-0.0704</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.583</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2119</v>
+        <v>-0.1913</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.357</v>
+        <v>-5.739</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>2.07</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6196</v>
+        <v>1.6497</v>
       </c>
       <c r="J52" t="n">
-        <v>35.6312</v>
+        <v>36.2934</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.57</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0121</v>
+        <v>1.0025</v>
       </c>
       <c r="J53" t="n">
-        <v>22.2662</v>
+        <v>22.055</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>1.36</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7361</v>
+        <v>0.7284</v>
       </c>
       <c r="J54" t="n">
-        <v>16.1942</v>
+        <v>16.0248</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>1.25</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5742</v>
+        <v>0.5717</v>
       </c>
       <c r="J55" t="n">
-        <v>12.6324</v>
+        <v>12.5774</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.86</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5165</v>
+        <v>-0.4842</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.363</v>
+        <v>-10.6524</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>0.85</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.171</v>
+        <v>-0.1554</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.762</v>
+        <v>-3.4188</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2442</v>
+        <v>-0.2294</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.3724</v>
+        <v>-5.0468</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.254</v>
+        <v>-0.2394</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.588</v>
+        <v>-5.2668</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4248</v>
+        <v>-0.4156</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.345599999999999</v>
+        <v>-9.1432</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>0.57</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4337</v>
+        <v>-0.4252</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.541399999999999</v>
+        <v>-9.3544</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3929</v>
+        <v>0.3893</v>
       </c>
       <c r="J62" t="n">
-        <v>14.1444</v>
+        <v>14.0148</v>
       </c>
     </row>
     <row r="63">
@@ -4823,10 +4823,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2859</v>
+        <v>0.2728</v>
       </c>
       <c r="J63" t="n">
-        <v>10.2924</v>
+        <v>9.8208</v>
       </c>
     </row>
     <row r="64">
@@ -4863,10 +4863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0987</v>
+        <v>-0.082</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.5532</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>0.93</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1112</v>
+        <v>-0.0935</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.0032</v>
+        <v>-3.366</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.71</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3381</v>
+        <v>-0.3226</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.1716</v>
+        <v>-11.6136</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.461</v>
+        <v>0.4025</v>
       </c>
       <c r="J67" t="n">
-        <v>16.596</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2639</v>
+        <v>0.212</v>
       </c>
       <c r="J68" t="n">
-        <v>9.500400000000001</v>
+        <v>7.632</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0516</v>
+        <v>0.0356</v>
       </c>
       <c r="J69" t="n">
-        <v>1.8576</v>
+        <v>1.2816</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1153</v>
+        <v>-0.097</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.1508</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.79</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2664</v>
+        <v>-0.2472</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.590400000000001</v>
+        <v>-8.8992</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.79</v>
       </c>
       <c r="I72" t="n">
-        <v>1.306</v>
+        <v>1.3091</v>
       </c>
       <c r="J72" t="n">
-        <v>32.65</v>
+        <v>32.7275</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.66</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1424</v>
+        <v>1.1356</v>
       </c>
       <c r="J73" t="n">
-        <v>28.56</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7429</v>
+        <v>0.7318</v>
       </c>
       <c r="J74" t="n">
-        <v>18.5725</v>
+        <v>18.295</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1929</v>
+        <v>-0.1637</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.8225</v>
+        <v>-4.0925</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>0.86</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5032</v>
+        <v>-0.4675</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.58</v>
+        <v>-11.6875</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6311</v>
+        <v>0.6115</v>
       </c>
       <c r="J77" t="n">
-        <v>15.7775</v>
+        <v>15.2875</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2069</v>
+        <v>-0.1892</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.1725</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.8</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2356</v>
+        <v>-0.2175</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.89</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.66</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3663</v>
+        <v>-0.3522</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.157500000000001</v>
+        <v>-8.805</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.49</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5162</v>
+        <v>-0.5178</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.905</v>
+        <v>-12.945</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8961</v>
+        <v>0.8784</v>
       </c>
       <c r="J82" t="n">
-        <v>25.9869</v>
+        <v>25.4736</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3053</v>
+        <v>0.2663</v>
       </c>
       <c r="J83" t="n">
-        <v>8.8537</v>
+        <v>7.7227</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.193</v>
+        <v>0.1614</v>
       </c>
       <c r="J84" t="n">
-        <v>5.597</v>
+        <v>4.6806</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.99</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.9169</v>
+        <v>-1.3804</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.76</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.952</v>
+        <v>-18.9863</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4386</v>
+        <v>0.381</v>
       </c>
       <c r="J87" t="n">
-        <v>12.7194</v>
+        <v>11.049</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3323</v>
+        <v>0.2794</v>
       </c>
       <c r="J88" t="n">
-        <v>9.636699999999999</v>
+        <v>8.102600000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0975</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.8275</v>
+        <v>-2.3519</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2101</v>
+        <v>-0.1895</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.0929</v>
+        <v>-5.4955</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2702</v>
+        <v>-0.2509</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.8358</v>
+        <v>-7.2761</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>0.98</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0188</v>
+        <v>-0.0112</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.4512</v>
+        <v>-0.2688</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>0.82</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2142</v>
+        <v>-0.1974</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.1408</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2241</v>
+        <v>-0.2071</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.3784</v>
+        <v>-4.9704</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2615</v>
+        <v>-0.2443</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.276</v>
+        <v>-5.8632</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.57</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4433</v>
+        <v>-0.4358</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.6392</v>
+        <v>-10.4592</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2916</v>
+        <v>1.3106</v>
       </c>
       <c r="J97" t="n">
-        <v>30.9984</v>
+        <v>31.4544</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.28</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7036</v>
+        <v>0.677</v>
       </c>
       <c r="J98" t="n">
-        <v>16.8864</v>
+        <v>16.248</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6028</v>
+        <v>0.5728</v>
       </c>
       <c r="J99" t="n">
-        <v>14.4672</v>
+        <v>13.7472</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.21</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5603</v>
+        <v>0.5293</v>
       </c>
       <c r="J100" t="n">
-        <v>13.4472</v>
+        <v>12.7032</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.92</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3355</v>
+        <v>-0.2965</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.052</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3168</v>
+        <v>0.2649</v>
       </c>
       <c r="J102" t="n">
-        <v>9.504</v>
+        <v>7.947</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.06</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1759</v>
+        <v>0.1374</v>
       </c>
       <c r="J103" t="n">
-        <v>5.277</v>
+        <v>4.122</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0235</v>
+        <v>-0.0173</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.705</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0235</v>
+        <v>-0.0173</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.705</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.66</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.381</v>
+        <v>-0.3687</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.43</v>
+        <v>-11.061</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8282</v>
+        <v>0.8042</v>
       </c>
       <c r="J107" t="n">
-        <v>24.846</v>
+        <v>24.126</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7875</v>
+        <v>0.7605</v>
       </c>
       <c r="J108" t="n">
-        <v>23.625</v>
+        <v>22.815</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4176</v>
+        <v>0.38</v>
       </c>
       <c r="J109" t="n">
-        <v>12.528</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3201</v>
+        <v>0.285</v>
       </c>
       <c r="J110" t="n">
-        <v>9.603</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6142</v>
+        <v>-0.5782</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.426</v>
+        <v>-17.346</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>1.75</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3983</v>
+        <v>1.4231</v>
       </c>
       <c r="J112" t="n">
-        <v>33.5592</v>
+        <v>34.1544</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>1.72</v>
       </c>
       <c r="I113" t="n">
-        <v>1.3608</v>
+        <v>1.3833</v>
       </c>
       <c r="J113" t="n">
-        <v>32.6592</v>
+        <v>33.1992</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5899</v>
+        <v>0.5631</v>
       </c>
       <c r="J114" t="n">
-        <v>14.1576</v>
+        <v>13.5144</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3618</v>
+        <v>0.3299</v>
       </c>
       <c r="J115" t="n">
-        <v>8.683199999999999</v>
+        <v>7.9176</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.93</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.322</v>
+        <v>-0.2863</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.728</v>
+        <v>-6.8712</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4285</v>
+        <v>0.3807</v>
       </c>
       <c r="J117" t="n">
-        <v>10.284</v>
+        <v>9.136799999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1516</v>
+        <v>-0.1359</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.6384</v>
+        <v>-3.2616</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>0.74</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2901</v>
+        <v>-0.2729</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.9624</v>
+        <v>-6.5496</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>0.66</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3636</v>
+        <v>-0.3495</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.7264</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.54</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4704</v>
+        <v>-0.4658</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.2896</v>
+        <v>-11.1792</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4774</v>
+        <v>0.4194</v>
       </c>
       <c r="J122" t="n">
-        <v>14.322</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1305</v>
+        <v>0.0984</v>
       </c>
       <c r="J123" t="n">
-        <v>3.915</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.99</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0232</v>
+        <v>-0.0171</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.696</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1875</v>
+        <v>-0.1672</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.625</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3442</v>
+        <v>-0.3289</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.326</v>
+        <v>-9.867000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6332</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J127" t="n">
-        <v>18.996</v>
+        <v>17.889</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.12</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3775</v>
+        <v>0.3375</v>
       </c>
       <c r="J128" t="n">
-        <v>11.325</v>
+        <v>10.125</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2477</v>
+        <v>0.2133</v>
       </c>
       <c r="J129" t="n">
-        <v>7.431</v>
+        <v>6.399</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1899</v>
+        <v>0.1599</v>
       </c>
       <c r="J130" t="n">
-        <v>5.697</v>
+        <v>4.797</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3301</v>
+        <v>-0.288</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.903</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.79</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2181</v>
+        <v>1.2144</v>
       </c>
       <c r="J132" t="n">
-        <v>36.543</v>
+        <v>36.432</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>0.89</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1598</v>
+        <v>-0.1396</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.794</v>
+        <v>-4.188</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1818</v>
+        <v>-0.1612</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.454</v>
+        <v>-4.836</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.234</v>
+        <v>-0.2137</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.02</v>
+        <v>-6.411</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3308</v>
+        <v>-0.3149</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.923999999999999</v>
+        <v>-9.446999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.071</v>
+        <v>1.0802</v>
       </c>
       <c r="J137" t="n">
-        <v>32.13</v>
+        <v>32.406</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5601</v>
+        <v>0.5215</v>
       </c>
       <c r="J138" t="n">
-        <v>16.803</v>
+        <v>15.645</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0433</v>
+        <v>0.0323</v>
       </c>
       <c r="J139" t="n">
-        <v>1.299</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.283</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4652</v>
+        <v>-0.423</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.956</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1961</v>
+        <v>1.2109</v>
       </c>
       <c r="J142" t="n">
-        <v>29.9025</v>
+        <v>30.2725</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9082</v>
+        <v>0.8923</v>
       </c>
       <c r="J143" t="n">
-        <v>22.705</v>
+        <v>22.3075</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4778</v>
+        <v>0.4438</v>
       </c>
       <c r="J144" t="n">
-        <v>11.945</v>
+        <v>11.095</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>1.07</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2263</v>
+        <v>0.1968</v>
       </c>
       <c r="J145" t="n">
-        <v>5.6575</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4347</v>
+        <v>-0.3943</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.8675</v>
+        <v>-9.8575</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5285</v>
+        <v>0.4755</v>
       </c>
       <c r="J147" t="n">
-        <v>13.2125</v>
+        <v>11.8875</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>0.91</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1249</v>
+        <v>-0.1092</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.1225</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1994</v>
+        <v>-0.1807</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.985</v>
+        <v>-4.5175</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3524</v>
+        <v>-0.3374</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.81</v>
+        <v>-8.435</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3887</v>
+        <v>-0.3764</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.717499999999999</v>
+        <v>-9.41</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4707</v>
+        <v>0.4163</v>
       </c>
       <c r="J152" t="n">
-        <v>10.8261</v>
+        <v>9.5749</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3223</v>
+        <v>0.2721</v>
       </c>
       <c r="J153" t="n">
-        <v>7.4129</v>
+        <v>6.2583</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2887</v>
+        <v>-0.2704</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.6401</v>
+        <v>-6.2192</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.317</v>
+        <v>-0.2998</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.291</v>
+        <v>-6.8954</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4434</v>
+        <v>-0.4365</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.1982</v>
+        <v>-10.0395</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9618</v>
       </c>
       <c r="J157" t="n">
-        <v>22.2686</v>
+        <v>22.1214</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>1.38</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8954</v>
+        <v>0.8807</v>
       </c>
       <c r="J158" t="n">
-        <v>20.5942</v>
+        <v>20.2561</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>1.35</v>
       </c>
       <c r="I159" t="n">
-        <v>0.838</v>
+        <v>0.8193</v>
       </c>
       <c r="J159" t="n">
-        <v>19.274</v>
+        <v>18.8439</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>1.28</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7018</v>
+        <v>0.6762</v>
       </c>
       <c r="J160" t="n">
-        <v>16.1414</v>
+        <v>15.5526</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2187</v>
+        <v>-0.1856</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.0301</v>
+        <v>-4.2688</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.84</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5403</v>
+        <v>1.5788</v>
       </c>
       <c r="J162" t="n">
-        <v>41.5881</v>
+        <v>42.6276</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8065</v>
+        <v>0.7839</v>
       </c>
       <c r="J163" t="n">
-        <v>21.7755</v>
+        <v>21.1653</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5633</v>
+        <v>0.5312</v>
       </c>
       <c r="J164" t="n">
-        <v>15.2091</v>
+        <v>14.3424</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.98</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1408</v>
+        <v>-0.1139</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.8016</v>
+        <v>-3.0753</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6079</v>
+        <v>-0.574</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.4133</v>
+        <v>-15.498</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1278</v>
+        <v>0.0973</v>
       </c>
       <c r="J167" t="n">
-        <v>3.4506</v>
+        <v>2.6271</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>0.91</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1249</v>
+        <v>-0.1092</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.3723</v>
+        <v>-2.9484</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>0.89</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1476</v>
+        <v>-0.1308</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.9852</v>
+        <v>-3.5316</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2778</v>
+        <v>-0.2592</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.5006</v>
+        <v>-6.9984</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.71</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3248</v>
+        <v>-0.3081</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.769600000000001</v>
+        <v>-8.3187</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.82</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4655</v>
+        <v>1.4946</v>
       </c>
       <c r="J172" t="n">
-        <v>27.8445</v>
+        <v>28.3974</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1051</v>
+        <v>1.1211</v>
       </c>
       <c r="J173" t="n">
-        <v>20.9969</v>
+        <v>21.3009</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.47</v>
       </c>
       <c r="I174" t="n">
-        <v>1.0249</v>
+        <v>1.034</v>
       </c>
       <c r="J174" t="n">
-        <v>19.4731</v>
+        <v>19.646</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8566</v>
+        <v>0.8475</v>
       </c>
       <c r="J175" t="n">
-        <v>16.2754</v>
+        <v>16.1025</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.13</v>
+        <v>0.1014</v>
       </c>
       <c r="J176" t="n">
-        <v>2.47</v>
+        <v>1.9266</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>0.86</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1366</v>
+        <v>-0.1168</v>
       </c>
       <c r="J177" t="n">
-        <v>-2.5954</v>
+        <v>-2.2192</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>0.79</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2151</v>
+        <v>-0.1993</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.0869</v>
+        <v>-3.7867</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3346</v>
+        <v>-0.3244</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.3574</v>
+        <v>-6.1636</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4825</v>
+        <v>-0.4789</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.1675</v>
+        <v>-9.0991</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.26</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6934</v>
+        <v>-0.7225</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.1746</v>
+        <v>-13.7275</v>
       </c>
     </row>
   </sheetData>
